--- a/sim-output/IndianWells-2026_results.xlsx
+++ b/sim-output/IndianWells-2026_results.xlsx
@@ -58,12 +58,12 @@
     <t>Jannik Sinner</t>
   </si>
   <si>
+    <t>Novak Djokovic</t>
+  </si>
+  <si>
     <t>Alexander Zverev</t>
   </si>
   <si>
-    <t>Novak Djokovic</t>
-  </si>
-  <si>
     <t>Taylor Fritz</t>
   </si>
   <si>
@@ -79,24 +79,24 @@
     <t>Jack Draper</t>
   </si>
   <si>
+    <t>Jakub Mensik</t>
+  </si>
+  <si>
+    <t>Learner Tien</t>
+  </si>
+  <si>
     <t>Felix Auger Aliassime</t>
   </si>
   <si>
-    <t>Jakub Mensik</t>
-  </si>
-  <si>
-    <t>Learner Tien</t>
-  </si>
-  <si>
     <t>Lorenzo Musetti</t>
   </si>
   <si>
+    <t>Arthur Fils</t>
+  </si>
+  <si>
     <t>Alexander Bublik</t>
   </si>
   <si>
-    <t>Arthur Fils</t>
-  </si>
-  <si>
     <t>Casper Ruud</t>
   </si>
   <si>
@@ -139,405 +139,405 @@
     <t>Joao Fonseca</t>
   </si>
   <si>
+    <t>Hubert Hurkacz</t>
+  </si>
+  <si>
     <t>Francisco Cerundolo</t>
   </si>
   <si>
-    <t>Hubert Hurkacz</t>
-  </si>
-  <si>
     <t>Matteo Berrettini</t>
   </si>
   <si>
     <t>Arthur Rinderknech</t>
   </si>
   <si>
+    <t>Stefanos Tsitsipas</t>
+  </si>
+  <si>
     <t>Miomir Kecmanovic</t>
   </si>
   <si>
-    <t>Stefanos Tsitsipas</t>
-  </si>
-  <si>
     <t>Luciano Darderi</t>
   </si>
   <si>
+    <t>Fabian Marozsan</t>
+  </si>
+  <si>
+    <t>Denis Shapovalov</t>
+  </si>
+  <si>
     <t>Alex Michelsen</t>
   </si>
   <si>
-    <t>Denis Shapovalov</t>
-  </si>
-  <si>
-    <t>Fabian Marozsan</t>
+    <t>Grigor Dimitrov</t>
   </si>
   <si>
     <t>Corentin Moutet</t>
   </si>
   <si>
-    <t>Grigor Dimitrov</t>
-  </si>
-  <si>
     <t>Tomas Martin Etcheverry</t>
   </si>
   <si>
     <t>Marin Cilic</t>
   </si>
   <si>
+    <t>Marcos Giron</t>
+  </si>
+  <si>
     <t>Jenson Brooksby</t>
   </si>
   <si>
-    <t>Marcos Giron</t>
+    <t>Nuno Borges</t>
   </si>
   <si>
     <t>Raphael Collignon</t>
   </si>
   <si>
+    <t>Rafael Jodar</t>
+  </si>
+  <si>
+    <t>Botic Van De Zandschulp</t>
+  </si>
+  <si>
+    <t>Sebastian Baez</t>
+  </si>
+  <si>
     <t>Michael Zheng</t>
   </si>
   <si>
-    <t>Botic Van De Zandschulp</t>
-  </si>
-  <si>
-    <t>Rafael Jodar</t>
-  </si>
-  <si>
-    <t>Sebastian Baez</t>
-  </si>
-  <si>
-    <t>Nuno Borges</t>
-  </si>
-  <si>
     <t>Zizou Bergs</t>
   </si>
   <si>
     <t>Zachary Svajda</t>
   </si>
   <si>
+    <t>Alejandro Tabilo</t>
+  </si>
+  <si>
+    <t>Kamil Majchrzak</t>
+  </si>
+  <si>
+    <t>Gabriel Diallo</t>
+  </si>
+  <si>
     <t>Reilly Opelka</t>
   </si>
   <si>
-    <t>Kamil Majchrzak</t>
-  </si>
-  <si>
     <t>Ethan Quinn</t>
   </si>
   <si>
-    <t>Alejandro Tabilo</t>
-  </si>
-  <si>
     <t>Dino Prizmic</t>
   </si>
   <si>
-    <t>Gabriel Diallo</t>
-  </si>
-  <si>
     <t>Martin Damm</t>
   </si>
   <si>
+    <t>Benjamin Bonzi</t>
+  </si>
+  <si>
+    <t>Jan Lennard Struff</t>
+  </si>
+  <si>
     <t>Giovanni Mpetshi Perricard</t>
   </si>
   <si>
+    <t>Alexei Popyrin</t>
+  </si>
+  <si>
     <t>Marton Fucsovics</t>
   </si>
   <si>
     <t>Quentin Halys</t>
   </si>
   <si>
-    <t>Benjamin Bonzi</t>
-  </si>
-  <si>
-    <t>Alexei Popyrin</t>
+    <t>Arthur Cazaux</t>
   </si>
   <si>
     <t>Mackenzie Mcdonald</t>
   </si>
   <si>
+    <t>Adrian Mannarino</t>
+  </si>
+  <si>
     <t>Gael Monfils</t>
   </si>
   <si>
+    <t>Francesco Maestrelli</t>
+  </si>
+  <si>
+    <t>Mattia Bellucci</t>
+  </si>
+  <si>
+    <t>Sho Shimabukuro</t>
+  </si>
+  <si>
+    <t>Jacob Fearnley</t>
+  </si>
+  <si>
+    <t>Christopher Oconnell</t>
+  </si>
+  <si>
+    <t>Terence Atmane</t>
+  </si>
+  <si>
+    <t>Alexander Shevchenko</t>
+  </si>
+  <si>
     <t>Rinky Hijikata</t>
   </si>
   <si>
-    <t>Terence Atmane</t>
-  </si>
-  <si>
-    <t>Jan Lennard Struff</t>
-  </si>
-  <si>
-    <t>Adrian Mannarino</t>
-  </si>
-  <si>
     <t>Francisco Comesana</t>
   </si>
   <si>
-    <t>Arthur Cazaux</t>
-  </si>
-  <si>
-    <t>Mattia Bellucci</t>
+    <t>Valentin Royer</t>
   </si>
   <si>
     <t>Matteo Arnaldi</t>
   </si>
   <si>
+    <t>Emilio Nava</t>
+  </si>
+  <si>
+    <t>Juan Manuel Cerundolo</t>
+  </si>
+  <si>
     <t>Aleksandar Kovacevic</t>
   </si>
   <si>
-    <t>Valentin Royer</t>
-  </si>
-  <si>
-    <t>Jacob Fearnley</t>
-  </si>
-  <si>
-    <t>Francesco Maestrelli</t>
+    <t>Mariano Navone</t>
+  </si>
+  <si>
+    <t>Dalibor Svrcina</t>
   </si>
   <si>
     <t>Roberto Bautista Agut</t>
   </si>
   <si>
-    <t>Sho Shimabukuro</t>
-  </si>
-  <si>
-    <t>Christopher Oconnell</t>
-  </si>
-  <si>
     <t>Chun Hsin Tseng</t>
   </si>
   <si>
+    <t>Damir Dzumhur</t>
+  </si>
+  <si>
+    <t>Camilo Ugo Carabelli</t>
+  </si>
+  <si>
+    <t>James Duckworth</t>
+  </si>
+  <si>
+    <t>Bye</t>
+  </si>
+  <si>
+    <t>Daniel Merida Aguilar</t>
+  </si>
+  <si>
+    <t>Tristan Schoolkate</t>
+  </si>
+  <si>
     <t>Alexis Galarneau</t>
   </si>
   <si>
-    <t>Dalibor Svrcina</t>
-  </si>
-  <si>
-    <t>Juan Manuel Cerundolo</t>
-  </si>
-  <si>
-    <t>Emilio Nava</t>
-  </si>
-  <si>
-    <t>Alexander Shevchenko</t>
-  </si>
-  <si>
-    <t>Daniel Merida Aguilar</t>
-  </si>
-  <si>
-    <t>Tristan Schoolkate</t>
-  </si>
-  <si>
-    <t>Camilo Ugo Carabelli</t>
+    <t>Daniel Altmaier</t>
   </si>
   <si>
     <t>Adam Walton</t>
   </si>
   <si>
-    <t>Bye</t>
-  </si>
-  <si>
-    <t>Damir Dzumhur</t>
-  </si>
-  <si>
-    <t>Daniel Altmaier</t>
-  </si>
-  <si>
-    <t>Mariano Navone</t>
-  </si>
-  <si>
-    <t>James Duckworth</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
     <t>Q4</t>
   </si>
   <si>
+    <t>Q2</t>
+  </si>
+  <si>
     <t>Q3</t>
   </si>
   <si>
-    <t>Q2</t>
-  </si>
-  <si>
     <t>+121</t>
   </si>
   <si>
     <t>+174</t>
   </si>
   <si>
-    <t>+3420</t>
-  </si>
-  <si>
-    <t>+3435</t>
-  </si>
-  <si>
-    <t>+5561</t>
-  </si>
-  <si>
-    <t>+6025</t>
-  </si>
-  <si>
-    <t>+8899</t>
-  </si>
-  <si>
-    <t>+12384</t>
-  </si>
-  <si>
-    <t>+13100</t>
-  </si>
-  <si>
-    <t>+15385</t>
-  </si>
-  <si>
-    <t>+15631</t>
-  </si>
-  <si>
-    <t>+16158</t>
-  </si>
-  <si>
-    <t>+16572</t>
-  </si>
-  <si>
-    <t>+19608</t>
-  </si>
-  <si>
-    <t>+19892</t>
-  </si>
-  <si>
-    <t>+28149</t>
-  </si>
-  <si>
-    <t>+29294</t>
-  </si>
-  <si>
-    <t>+30850</t>
-  </si>
-  <si>
-    <t>+33435</t>
-  </si>
-  <si>
-    <t>+38660</t>
-  </si>
-  <si>
-    <t>+49726</t>
-  </si>
-  <si>
-    <t>+74084</t>
-  </si>
-  <si>
-    <t>+76294</t>
-  </si>
-  <si>
-    <t>+83026</t>
-  </si>
-  <si>
-    <t>+85443</t>
-  </si>
-  <si>
-    <t>+119374</t>
-  </si>
-  <si>
-    <t>+148931</t>
-  </si>
-  <si>
-    <t>+162502</t>
-  </si>
-  <si>
-    <t>+181718</t>
-  </si>
-  <si>
-    <t>+197920</t>
-  </si>
-  <si>
-    <t>+217765</t>
-  </si>
-  <si>
-    <t>+260997</t>
-  </si>
-  <si>
-    <t>+306648</t>
-  </si>
-  <si>
-    <t>+352013</t>
-  </si>
-  <si>
-    <t>+401506</t>
+    <t>+3419</t>
+  </si>
+  <si>
+    <t>+3428</t>
+  </si>
+  <si>
+    <t>+5476</t>
+  </si>
+  <si>
+    <t>+6010</t>
+  </si>
+  <si>
+    <t>+8765</t>
+  </si>
+  <si>
+    <t>+12616</t>
+  </si>
+  <si>
+    <t>+13080</t>
+  </si>
+  <si>
+    <t>+15668</t>
+  </si>
+  <si>
+    <t>+15869</t>
+  </si>
+  <si>
+    <t>+15967</t>
+  </si>
+  <si>
+    <t>+16597</t>
+  </si>
+  <si>
+    <t>+19698</t>
+  </si>
+  <si>
+    <t>+20651</t>
+  </si>
+  <si>
+    <t>+27267</t>
+  </si>
+  <si>
+    <t>+29200</t>
+  </si>
+  <si>
+    <t>+29644</t>
+  </si>
+  <si>
+    <t>+34182</t>
+  </si>
+  <si>
+    <t>+39208</t>
+  </si>
+  <si>
+    <t>+50946</t>
+  </si>
+  <si>
+    <t>+74638</t>
+  </si>
+  <si>
+    <t>+78578</t>
+  </si>
+  <si>
+    <t>+80221</t>
+  </si>
+  <si>
+    <t>+81069</t>
+  </si>
+  <si>
+    <t>+115107</t>
+  </si>
+  <si>
+    <t>+138982</t>
+  </si>
+  <si>
+    <t>+169679</t>
+  </si>
+  <si>
+    <t>+178791</t>
+  </si>
+  <si>
+    <t>+203152</t>
+  </si>
+  <si>
+    <t>+203982</t>
+  </si>
+  <si>
+    <t>+254353</t>
+  </si>
+  <si>
+    <t>+332126</t>
+  </si>
+  <si>
+    <t>+378688</t>
+  </si>
+  <si>
+    <t>+381579</t>
   </si>
   <si>
     <t>+482992</t>
   </si>
   <si>
-    <t>+497412</t>
-  </si>
-  <si>
-    <t>+529001</t>
+    <t>+512721</t>
   </si>
   <si>
     <t>+571329</t>
   </si>
   <si>
-    <t>+598702</t>
+    <t>+602310</t>
   </si>
   <si>
     <t>+609656</t>
   </si>
   <si>
-    <t>+632811</t>
-  </si>
-  <si>
-    <t>+735194</t>
-  </si>
-  <si>
-    <t>+746169</t>
-  </si>
-  <si>
-    <t>+833233</t>
-  </si>
-  <si>
-    <t>+1086857</t>
-  </si>
-  <si>
-    <t>+1190376</t>
+    <t>+694344</t>
+  </si>
+  <si>
+    <t>+704125</t>
+  </si>
+  <si>
+    <t>+757476</t>
+  </si>
+  <si>
+    <t>+775094</t>
+  </si>
+  <si>
+    <t>+999900</t>
   </si>
   <si>
     <t>+1204719</t>
   </si>
   <si>
-    <t>+1219412</t>
-  </si>
-  <si>
     <t>+1234468</t>
   </si>
   <si>
-    <t>+1351251</t>
-  </si>
-  <si>
-    <t>+1587202</t>
-  </si>
-  <si>
-    <t>+1999900</t>
-  </si>
-  <si>
-    <t>+2380852</t>
+    <t>+1265723</t>
+  </si>
+  <si>
+    <t>+1562400</t>
+  </si>
+  <si>
+    <t>+1639244</t>
+  </si>
+  <si>
+    <t>+1666567</t>
+  </si>
+  <si>
+    <t>+1724038</t>
+  </si>
+  <si>
+    <t>+2173813</t>
   </si>
   <si>
     <t>+2438924</t>
   </si>
   <si>
-    <t>+2564003</t>
-  </si>
-  <si>
     <t>+2631479</t>
   </si>
   <si>
-    <t>+2777678</t>
+    <t>+2857043</t>
+  </si>
+  <si>
+    <t>+3030203</t>
+  </si>
+  <si>
+    <t>+3124900</t>
+  </si>
+  <si>
+    <t>+3448176</t>
+  </si>
+  <si>
+    <t>+3571329</t>
   </si>
   <si>
     <t>+3846054</t>
   </si>
   <si>
-    <t>+4545355</t>
-  </si>
-  <si>
-    <t>+4761805</t>
-  </si>
-  <si>
     <t>+4999900</t>
   </si>
   <si>
@@ -550,7 +550,7 @@
     <t>+7142757</t>
   </si>
   <si>
-    <t>+8333233</t>
+    <t>+7692208</t>
   </si>
   <si>
     <t>+9090809</t>
@@ -559,13 +559,13 @@
     <t>+9999900</t>
   </si>
   <si>
-    <t>+12499900</t>
+    <t>+11111011</t>
   </si>
   <si>
     <t>+14285614</t>
   </si>
   <si>
-    <t>+16666567</t>
+    <t>+19999900</t>
   </si>
   <si>
     <t>+24999900</t>
@@ -996,19 +996,19 @@
         <v>95.23999999999999</v>
       </c>
       <c r="G2">
-        <v>90.76000000000001</v>
+        <v>90.72</v>
       </c>
       <c r="H2">
-        <v>84.52</v>
+        <v>84.44</v>
       </c>
       <c r="I2">
-        <v>77.14</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J2">
-        <v>66.98</v>
+        <v>66.95</v>
       </c>
       <c r="K2">
-        <v>45.19</v>
+        <v>45.16</v>
       </c>
       <c r="L2" t="s">
         <v>113</v>
@@ -1028,22 +1028,22 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>97.27</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="G3">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H3">
-        <v>82.3</v>
+        <v>82.37</v>
       </c>
       <c r="I3">
-        <v>71.87</v>
+        <v>71.92</v>
       </c>
       <c r="J3">
-        <v>62.67</v>
+        <v>62.68</v>
       </c>
       <c r="K3">
-        <v>36.51</v>
+        <v>36.52</v>
       </c>
       <c r="L3" t="s">
         <v>114</v>
@@ -1054,7 +1054,7 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
         <v>111</v>
@@ -1063,19 +1063,19 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>79.15000000000001</v>
+        <v>83.78</v>
       </c>
       <c r="G4">
-        <v>61.51</v>
+        <v>66.91</v>
       </c>
       <c r="H4">
-        <v>45.29</v>
+        <v>47.14</v>
       </c>
       <c r="I4">
-        <v>30.01</v>
+        <v>28.23</v>
       </c>
       <c r="J4">
-        <v>9.5</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K4">
         <v>2.84</v>
@@ -1089,7 +1089,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
         <v>112</v>
@@ -1098,19 +1098,19 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>83.8</v>
+        <v>79.13</v>
       </c>
       <c r="G5">
-        <v>67.01000000000001</v>
+        <v>61.43</v>
       </c>
       <c r="H5">
-        <v>47.2</v>
+        <v>45.29</v>
       </c>
       <c r="I5">
-        <v>28.23</v>
+        <v>30.06</v>
       </c>
       <c r="J5">
-        <v>8.02</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="K5">
         <v>2.83</v>
@@ -1127,28 +1127,28 @@
         <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E6">
         <v>100</v>
       </c>
       <c r="F6">
-        <v>87.53</v>
+        <v>87.48</v>
       </c>
       <c r="G6">
-        <v>63.07</v>
+        <v>63.11</v>
       </c>
       <c r="H6">
-        <v>37.03</v>
+        <v>37.05</v>
       </c>
       <c r="I6">
-        <v>21.15</v>
+        <v>21.16</v>
       </c>
       <c r="J6">
-        <v>5.49</v>
+        <v>5.5</v>
       </c>
       <c r="K6">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="L6" t="s">
         <v>117</v>
@@ -1162,28 +1162,28 @@
         <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7">
         <v>100</v>
       </c>
       <c r="F7">
-        <v>78.33</v>
+        <v>78.37</v>
       </c>
       <c r="G7">
-        <v>55.52</v>
+        <v>55.55</v>
       </c>
       <c r="H7">
-        <v>32.86</v>
+        <v>32.82</v>
       </c>
       <c r="I7">
-        <v>18.98</v>
+        <v>18.94</v>
       </c>
       <c r="J7">
         <v>4.98</v>
       </c>
       <c r="K7">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="L7" t="s">
         <v>118</v>
@@ -1203,22 +1203,22 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>78.03</v>
+        <v>77.98</v>
       </c>
       <c r="G8">
-        <v>47.44</v>
+        <v>47.48</v>
       </c>
       <c r="H8">
-        <v>30.05</v>
+        <v>30.03</v>
       </c>
       <c r="I8">
-        <v>7.45</v>
+        <v>7.41</v>
       </c>
       <c r="J8">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="K8">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="L8" t="s">
         <v>119</v>
@@ -1238,22 +1238,22 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>61.48</v>
+        <v>61.4</v>
       </c>
       <c r="G9">
-        <v>45.03</v>
+        <v>44.97</v>
       </c>
       <c r="H9">
-        <v>29.82</v>
+        <v>29.71</v>
       </c>
       <c r="I9">
-        <v>5.94</v>
+        <v>5.92</v>
       </c>
       <c r="J9">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="K9">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="L9" t="s">
         <v>120</v>
@@ -1267,22 +1267,22 @@
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10">
         <v>100</v>
       </c>
       <c r="F10">
-        <v>74.34999999999999</v>
+        <v>74.33</v>
       </c>
       <c r="G10">
-        <v>54.23</v>
+        <v>54.18</v>
       </c>
       <c r="H10">
-        <v>26.63</v>
+        <v>26.69</v>
       </c>
       <c r="I10">
-        <v>12.91</v>
+        <v>12.95</v>
       </c>
       <c r="J10">
         <v>2.82</v>
@@ -1299,31 +1299,31 @@
         <v>21</v>
       </c>
       <c r="C11">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E11">
         <v>100</v>
       </c>
       <c r="F11">
-        <v>81.04000000000001</v>
+        <v>74.92</v>
       </c>
       <c r="G11">
-        <v>48.75</v>
+        <v>48.28</v>
       </c>
       <c r="H11">
-        <v>26.25</v>
+        <v>24.2</v>
       </c>
       <c r="I11">
-        <v>13.18</v>
+        <v>5.24</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="K11">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="L11" t="s">
         <v>122</v>
@@ -1334,7 +1334,7 @@
         <v>22</v>
       </c>
       <c r="C12">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
         <v>110</v>
@@ -1343,22 +1343,22 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>74.84999999999999</v>
+        <v>81.73</v>
       </c>
       <c r="G12">
-        <v>48.32</v>
+        <v>41.58</v>
       </c>
       <c r="H12">
-        <v>24.29</v>
+        <v>24.18</v>
       </c>
       <c r="I12">
-        <v>5.27</v>
+        <v>5.21</v>
       </c>
       <c r="J12">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="K12">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="L12" t="s">
         <v>123</v>
@@ -1369,28 +1369,28 @@
         <v>23</v>
       </c>
       <c r="C13">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E13">
         <v>100</v>
       </c>
       <c r="F13">
-        <v>81.7</v>
+        <v>81</v>
       </c>
       <c r="G13">
-        <v>41.58</v>
+        <v>48.78</v>
       </c>
       <c r="H13">
-        <v>24.13</v>
+        <v>26.32</v>
       </c>
       <c r="I13">
-        <v>5.19</v>
+        <v>13.2</v>
       </c>
       <c r="J13">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="K13">
         <v>0.62</v>
@@ -1407,22 +1407,22 @@
         <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E14">
         <v>100</v>
       </c>
       <c r="F14">
-        <v>79.03</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="G14">
-        <v>45.06</v>
+        <v>45.07</v>
       </c>
       <c r="H14">
-        <v>24.92</v>
+        <v>24.87</v>
       </c>
       <c r="I14">
-        <v>12.52</v>
+        <v>12.48</v>
       </c>
       <c r="J14">
         <v>2.81</v>
@@ -1439,28 +1439,28 @@
         <v>25</v>
       </c>
       <c r="C15">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E15">
         <v>100</v>
       </c>
       <c r="F15">
-        <v>74.56999999999999</v>
+        <v>78.42</v>
       </c>
       <c r="G15">
-        <v>55.3</v>
+        <v>42.93</v>
       </c>
       <c r="H15">
-        <v>28.93</v>
+        <v>23.19</v>
       </c>
       <c r="I15">
-        <v>4.92</v>
+        <v>11.32</v>
       </c>
       <c r="J15">
-        <v>2.05</v>
+        <v>2.46</v>
       </c>
       <c r="K15">
         <v>0.51</v>
@@ -1474,31 +1474,31 @@
         <v>26</v>
       </c>
       <c r="C16">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E16">
         <v>100</v>
       </c>
       <c r="F16">
-        <v>78.48999999999999</v>
+        <v>74.48</v>
       </c>
       <c r="G16">
-        <v>42.98</v>
+        <v>55.22</v>
       </c>
       <c r="H16">
-        <v>23.16</v>
+        <v>28.9</v>
       </c>
       <c r="I16">
-        <v>11.33</v>
+        <v>4.95</v>
       </c>
       <c r="J16">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="K16">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="L16" t="s">
         <v>127</v>
@@ -1518,22 +1518,22 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>79.08</v>
+        <v>79.09</v>
       </c>
       <c r="G17">
-        <v>51.92</v>
+        <v>52.06</v>
       </c>
       <c r="H17">
-        <v>7.34</v>
+        <v>7.39</v>
       </c>
       <c r="I17">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="J17">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="K17">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="L17" t="s">
         <v>128</v>
@@ -1547,25 +1547,25 @@
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E18">
         <v>100</v>
       </c>
       <c r="F18">
-        <v>73.87</v>
+        <v>73.77</v>
       </c>
       <c r="G18">
-        <v>38.25</v>
+        <v>38.18</v>
       </c>
       <c r="H18">
-        <v>19.06</v>
+        <v>19</v>
       </c>
       <c r="I18">
-        <v>8.82</v>
+        <v>8.81</v>
       </c>
       <c r="J18">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="K18">
         <v>0.34</v>
@@ -1588,22 +1588,22 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>71.01000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="G19">
-        <v>42.23</v>
+        <v>42.12</v>
       </c>
       <c r="H19">
-        <v>6.9</v>
+        <v>6.88</v>
       </c>
       <c r="I19">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="J19">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="K19">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="L19" t="s">
         <v>130</v>
@@ -1617,28 +1617,28 @@
         <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E20">
         <v>100</v>
       </c>
       <c r="F20">
-        <v>68.25</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="G20">
-        <v>40.34</v>
+        <v>40.45</v>
       </c>
       <c r="H20">
-        <v>17.05</v>
+        <v>17.1</v>
       </c>
       <c r="I20">
-        <v>8.06</v>
+        <v>8.09</v>
       </c>
       <c r="J20">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="K20">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="L20" t="s">
         <v>131</v>
@@ -1655,25 +1655,25 @@
         <v>109</v>
       </c>
       <c r="E21">
-        <v>77.20999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="F21">
-        <v>34.18</v>
+        <v>34.27</v>
       </c>
       <c r="G21">
-        <v>23.5</v>
+        <v>23.51</v>
       </c>
       <c r="H21">
-        <v>14.32</v>
+        <v>14.39</v>
       </c>
       <c r="I21">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="J21">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="K21">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="L21" t="s">
         <v>132</v>
@@ -1687,22 +1687,22 @@
         <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E22">
         <v>100</v>
       </c>
       <c r="F22">
-        <v>70.83</v>
+        <v>70.86</v>
       </c>
       <c r="G22">
-        <v>28.54</v>
+        <v>28.53</v>
       </c>
       <c r="H22">
-        <v>12.31</v>
+        <v>12.34</v>
       </c>
       <c r="I22">
-        <v>5.18</v>
+        <v>5.19</v>
       </c>
       <c r="J22">
         <v>0.92</v>
@@ -1728,13 +1728,13 @@
         <v>100</v>
       </c>
       <c r="F23">
-        <v>61.64</v>
+        <v>61.61</v>
       </c>
       <c r="G23">
-        <v>28.19</v>
+        <v>28.25</v>
       </c>
       <c r="H23">
-        <v>11.27</v>
+        <v>11.31</v>
       </c>
       <c r="I23">
         <v>1.88</v>
@@ -1757,25 +1757,25 @@
         <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E24">
         <v>100</v>
       </c>
       <c r="F24">
-        <v>62.72</v>
+        <v>62.76</v>
       </c>
       <c r="G24">
-        <v>31.53</v>
+        <v>31.38</v>
       </c>
       <c r="H24">
-        <v>11.73</v>
+        <v>11.72</v>
       </c>
       <c r="I24">
-        <v>4.92</v>
+        <v>4.9</v>
       </c>
       <c r="J24">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="K24">
         <v>0.13</v>
@@ -1792,25 +1792,25 @@
         <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E25">
         <v>100</v>
       </c>
       <c r="F25">
-        <v>70.51000000000001</v>
+        <v>70.38</v>
       </c>
       <c r="G25">
         <v>22.65</v>
       </c>
       <c r="H25">
-        <v>11.33</v>
+        <v>11.3</v>
       </c>
       <c r="I25">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="J25">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="K25">
         <v>0.12</v>
@@ -1827,22 +1827,22 @@
         <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E26">
         <v>100</v>
       </c>
       <c r="F26">
-        <v>64.55</v>
+        <v>64.53</v>
       </c>
       <c r="G26">
-        <v>23.64</v>
+        <v>23.65</v>
       </c>
       <c r="H26">
-        <v>9.49</v>
+        <v>9.5</v>
       </c>
       <c r="I26">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="J26">
         <v>0.59</v>
@@ -1868,22 +1868,22 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>52.58</v>
+        <v>52.53</v>
       </c>
       <c r="G27">
-        <v>25.09</v>
+        <v>25.17</v>
       </c>
       <c r="H27">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="I27">
         <v>1.29</v>
       </c>
       <c r="J27">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="K27">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="L27" t="s">
         <v>138</v>
@@ -1903,10 +1903,10 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>68.97</v>
+        <v>69</v>
       </c>
       <c r="G28">
-        <v>23.68</v>
+        <v>23.7</v>
       </c>
       <c r="H28">
         <v>11.4</v>
@@ -1938,16 +1938,16 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>63.16</v>
+        <v>63.24</v>
       </c>
       <c r="G29">
-        <v>28.37</v>
+        <v>28.29</v>
       </c>
       <c r="H29">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="I29">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="J29">
         <v>0.35</v>
@@ -1970,22 +1970,22 @@
         <v>110</v>
       </c>
       <c r="E30">
-        <v>59.88</v>
+        <v>59.81</v>
       </c>
       <c r="F30">
-        <v>30.77</v>
+        <v>30.8</v>
       </c>
       <c r="G30">
-        <v>15.11</v>
+        <v>15.14</v>
       </c>
       <c r="H30">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="I30">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="J30">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="K30">
         <v>0.06</v>
@@ -1999,28 +1999,28 @@
         <v>41</v>
       </c>
       <c r="C31">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E31">
-        <v>100</v>
+        <v>71.91</v>
       </c>
       <c r="F31">
-        <v>65.27</v>
+        <v>42.53</v>
       </c>
       <c r="G31">
-        <v>24.34</v>
+        <v>12.97</v>
       </c>
       <c r="H31">
-        <v>7.87</v>
+        <v>5.8</v>
       </c>
       <c r="I31">
-        <v>2.41</v>
+        <v>1.96</v>
       </c>
       <c r="J31">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="K31">
         <v>0.05</v>
@@ -2034,28 +2034,28 @@
         <v>42</v>
       </c>
       <c r="C32">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E32">
-        <v>71.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="F32">
-        <v>42.45</v>
+        <v>65.28</v>
       </c>
       <c r="G32">
-        <v>12.95</v>
+        <v>24.34</v>
       </c>
       <c r="H32">
-        <v>5.81</v>
+        <v>7.81</v>
       </c>
       <c r="I32">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="J32">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="K32">
         <v>0.05</v>
@@ -2072,22 +2072,22 @@
         <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E33">
         <v>66.39</v>
       </c>
       <c r="F33">
-        <v>16.11</v>
+        <v>16.15</v>
       </c>
       <c r="G33">
-        <v>8.630000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H33">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="I33">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="J33">
         <v>0.25</v>
@@ -2113,19 +2113,19 @@
         <v>100</v>
       </c>
       <c r="F34">
-        <v>60.3</v>
+        <v>60.34</v>
       </c>
       <c r="G34">
-        <v>4.5</v>
+        <v>4.51</v>
       </c>
       <c r="H34">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I34">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="J34">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="K34">
         <v>0.03</v>
@@ -2139,28 +2139,28 @@
         <v>45</v>
       </c>
       <c r="C35">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E35">
-        <v>75.73</v>
+        <v>51.38</v>
       </c>
       <c r="F35">
-        <v>32.55</v>
+        <v>29.29</v>
       </c>
       <c r="G35">
-        <v>14.12</v>
+        <v>2.76</v>
       </c>
       <c r="H35">
-        <v>4.43</v>
+        <v>1.26</v>
       </c>
       <c r="I35">
-        <v>1.57</v>
+        <v>0.47</v>
       </c>
       <c r="J35">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="K35">
         <v>0.03</v>
@@ -2174,31 +2174,31 @@
         <v>46</v>
       </c>
       <c r="C36">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E36">
-        <v>51.36</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="F36">
-        <v>29.32</v>
+        <v>32.52</v>
       </c>
       <c r="G36">
-        <v>2.8</v>
+        <v>14.09</v>
       </c>
       <c r="H36">
-        <v>1.29</v>
+        <v>4.4</v>
       </c>
       <c r="I36">
-        <v>0.48</v>
+        <v>1.55</v>
       </c>
       <c r="J36">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="K36">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L36" t="s">
         <v>147</v>
@@ -2218,19 +2218,19 @@
         <v>100</v>
       </c>
       <c r="F37">
-        <v>62.53</v>
+        <v>62.55</v>
       </c>
       <c r="G37">
         <v>22.34</v>
       </c>
       <c r="H37">
-        <v>7.2</v>
+        <v>7.22</v>
       </c>
       <c r="I37">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J37">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="K37">
         <v>0.02</v>
@@ -2244,28 +2244,28 @@
         <v>48</v>
       </c>
       <c r="C38">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E38">
-        <v>77.76000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="F38">
-        <v>31.79</v>
+        <v>20.19</v>
       </c>
       <c r="G38">
-        <v>9.380000000000001</v>
+        <v>10.88</v>
       </c>
       <c r="H38">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="I38">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="J38">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="K38">
         <v>0.02</v>
@@ -2285,19 +2285,19 @@
         <v>110</v>
       </c>
       <c r="E39">
-        <v>48.64</v>
+        <v>48.62</v>
       </c>
       <c r="F39">
-        <v>27.06</v>
+        <v>27.03</v>
       </c>
       <c r="G39">
         <v>2.46</v>
       </c>
       <c r="H39">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I39">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="J39">
         <v>0.14</v>
@@ -2306,7 +2306,7 @@
         <v>0.02</v>
       </c>
       <c r="L39" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2314,25 +2314,25 @@
         <v>50</v>
       </c>
       <c r="C40">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E40">
-        <v>67.77</v>
+        <v>77.81</v>
       </c>
       <c r="F40">
-        <v>20.2</v>
+        <v>31.78</v>
       </c>
       <c r="G40">
-        <v>10.81</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H40">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="I40">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="J40">
         <v>0.12</v>
@@ -2341,7 +2341,7 @@
         <v>0.02</v>
       </c>
       <c r="L40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2349,34 +2349,34 @@
         <v>51</v>
       </c>
       <c r="C41">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E41">
-        <v>100</v>
+        <v>62.51</v>
       </c>
       <c r="F41">
-        <v>47.36</v>
+        <v>3.43</v>
       </c>
       <c r="G41">
-        <v>11.31</v>
+        <v>1.88</v>
       </c>
       <c r="H41">
-        <v>4.12</v>
+        <v>0.84</v>
       </c>
       <c r="I41">
-        <v>1.09</v>
+        <v>0.33</v>
       </c>
       <c r="J41">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="K41">
         <v>0.02</v>
       </c>
       <c r="L41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2384,34 +2384,34 @@
         <v>52</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E42">
-        <v>62.58</v>
+        <v>100</v>
       </c>
       <c r="F42">
-        <v>3.42</v>
+        <v>47.31</v>
       </c>
       <c r="G42">
-        <v>1.87</v>
+        <v>11.27</v>
       </c>
       <c r="H42">
-        <v>0.85</v>
+        <v>4.1</v>
       </c>
       <c r="I42">
-        <v>0.33</v>
+        <v>1.06</v>
       </c>
       <c r="J42">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="K42">
         <v>0.02</v>
       </c>
       <c r="L42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2428,13 +2428,13 @@
         <v>100</v>
       </c>
       <c r="F43">
-        <v>43.62</v>
+        <v>43.68</v>
       </c>
       <c r="G43">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="H43">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="I43">
         <v>0.39</v>
@@ -2443,10 +2443,10 @@
         <v>0.12</v>
       </c>
       <c r="K43">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2460,19 +2460,19 @@
         <v>110</v>
       </c>
       <c r="E44">
-        <v>54.38</v>
+        <v>54.19</v>
       </c>
       <c r="F44">
-        <v>21.85</v>
+        <v>21.83</v>
       </c>
       <c r="G44">
-        <v>8.01</v>
+        <v>8.02</v>
       </c>
       <c r="H44">
         <v>2.51</v>
       </c>
       <c r="I44">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="J44">
         <v>0.1</v>
@@ -2481,7 +2481,7 @@
         <v>0.01</v>
       </c>
       <c r="L44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2489,34 +2489,34 @@
         <v>55</v>
       </c>
       <c r="C45">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E45">
-        <v>58.48</v>
+        <v>68.37</v>
       </c>
       <c r="F45">
-        <v>20.31</v>
+        <v>19.95</v>
       </c>
       <c r="G45">
-        <v>8.93</v>
+        <v>8.6</v>
       </c>
       <c r="H45">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="I45">
-        <v>0.86</v>
+        <v>0.31</v>
       </c>
       <c r="J45">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K45">
         <v>0.01</v>
       </c>
       <c r="L45" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2524,34 +2524,34 @@
         <v>56</v>
       </c>
       <c r="C46">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="D46" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E46">
-        <v>68.31999999999999</v>
+        <v>58.45</v>
       </c>
       <c r="F46">
-        <v>20.03</v>
+        <v>20.36</v>
       </c>
       <c r="G46">
-        <v>8.640000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="H46">
         <v>2.61</v>
       </c>
       <c r="I46">
-        <v>0.31</v>
+        <v>0.85</v>
       </c>
       <c r="J46">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="K46">
         <v>0.01</v>
       </c>
       <c r="L46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2559,25 +2559,25 @@
         <v>57</v>
       </c>
       <c r="C47">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E47">
-        <v>40.12</v>
+        <v>64.53</v>
       </c>
       <c r="F47">
-        <v>16.64</v>
+        <v>26.78</v>
       </c>
       <c r="G47">
-        <v>6.61</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H47">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="I47">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="J47">
         <v>0.07000000000000001</v>
@@ -2586,7 +2586,7 @@
         <v>0.01</v>
       </c>
       <c r="L47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2594,34 +2594,34 @@
         <v>58</v>
       </c>
       <c r="C48">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E48">
-        <v>58.42</v>
+        <v>40.19</v>
       </c>
       <c r="F48">
-        <v>16.4</v>
+        <v>16.67</v>
       </c>
       <c r="G48">
-        <v>8.74</v>
+        <v>6.64</v>
       </c>
       <c r="H48">
-        <v>2.71</v>
+        <v>0.68</v>
       </c>
       <c r="I48">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="J48">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K48">
         <v>0.01</v>
       </c>
       <c r="L48" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2629,25 +2629,25 @@
         <v>59</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="D49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E49">
-        <v>67.02</v>
+        <v>53.54</v>
       </c>
       <c r="F49">
-        <v>30.2</v>
+        <v>12.2</v>
       </c>
       <c r="G49">
-        <v>1.94</v>
+        <v>5.23</v>
       </c>
       <c r="H49">
-        <v>0.76</v>
+        <v>1.64</v>
       </c>
       <c r="I49">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="J49">
         <v>0.06</v>
@@ -2656,7 +2656,7 @@
         <v>0.01</v>
       </c>
       <c r="L49" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2664,34 +2664,34 @@
         <v>60</v>
       </c>
       <c r="C50">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E50">
-        <v>53.64</v>
+        <v>67.06</v>
       </c>
       <c r="F50">
-        <v>12.19</v>
+        <v>30.21</v>
       </c>
       <c r="G50">
-        <v>5.22</v>
+        <v>1.97</v>
       </c>
       <c r="H50">
-        <v>1.64</v>
+        <v>0.77</v>
       </c>
       <c r="I50">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="J50">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K50">
         <v>0.01</v>
       </c>
       <c r="L50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2702,22 +2702,22 @@
         <v>54</v>
       </c>
       <c r="D51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E51">
-        <v>66.44</v>
+        <v>66.47</v>
       </c>
       <c r="F51">
         <v>22.3</v>
       </c>
       <c r="G51">
-        <v>5.87</v>
+        <v>5.89</v>
       </c>
       <c r="H51">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="I51">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="J51">
         <v>0.05</v>
@@ -2726,7 +2726,7 @@
         <v>0.01</v>
       </c>
       <c r="L51" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2734,22 +2734,22 @@
         <v>62</v>
       </c>
       <c r="C52">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D52" t="s">
         <v>109</v>
       </c>
       <c r="E52">
-        <v>64.58</v>
+        <v>58.45</v>
       </c>
       <c r="F52">
-        <v>26.89</v>
+        <v>16.43</v>
       </c>
       <c r="G52">
-        <v>10.01</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H52">
-        <v>0.8</v>
+        <v>2.71</v>
       </c>
       <c r="I52">
         <v>0.26</v>
@@ -2761,7 +2761,7 @@
         <v>0.01</v>
       </c>
       <c r="L52" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2775,19 +2775,19 @@
         <v>110</v>
       </c>
       <c r="E53">
-        <v>55.68</v>
+        <v>55.67</v>
       </c>
       <c r="F53">
-        <v>17.28</v>
+        <v>17.32</v>
       </c>
       <c r="G53">
-        <v>6.9</v>
+        <v>6.89</v>
       </c>
       <c r="H53">
         <v>0.65</v>
       </c>
       <c r="I53">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="J53">
         <v>0.06</v>
@@ -2796,7 +2796,7 @@
         <v>0.01</v>
       </c>
       <c r="L53" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2810,16 +2810,16 @@
         <v>110</v>
       </c>
       <c r="E54">
-        <v>45.62</v>
+        <v>45.81</v>
       </c>
       <c r="F54">
-        <v>16.51</v>
+        <v>16.55</v>
       </c>
       <c r="G54">
-        <v>5.46</v>
+        <v>5.51</v>
       </c>
       <c r="H54">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="I54">
         <v>0.17</v>
@@ -2831,7 +2831,7 @@
         <v>0.01</v>
       </c>
       <c r="L54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -2839,25 +2839,25 @@
         <v>65</v>
       </c>
       <c r="C55">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E55">
-        <v>50.77</v>
+        <v>46.46</v>
       </c>
       <c r="F55">
-        <v>11.31</v>
+        <v>9.44</v>
       </c>
       <c r="G55">
         <v>3.71</v>
       </c>
       <c r="H55">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="I55">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="J55">
         <v>0.04</v>
@@ -2866,7 +2866,7 @@
         <v>0.01</v>
       </c>
       <c r="L55" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -2877,19 +2877,19 @@
         <v>35</v>
       </c>
       <c r="D56" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E56">
-        <v>51.42</v>
+        <v>51.44</v>
       </c>
       <c r="F56">
-        <v>8.529999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="G56">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="H56">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="I56">
         <v>0.31</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="L56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -2909,25 +2909,25 @@
         <v>67</v>
       </c>
       <c r="C57">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="D57" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E57">
-        <v>49.23</v>
+        <v>57.66</v>
       </c>
       <c r="F57">
-        <v>10.66</v>
+        <v>16.6</v>
       </c>
       <c r="G57">
-        <v>3.46</v>
+        <v>5.24</v>
       </c>
       <c r="H57">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="I57">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="J57">
         <v>0.04</v>
@@ -2944,28 +2944,28 @@
         <v>68</v>
       </c>
       <c r="C58">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="D58" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E58">
-        <v>46.36</v>
+        <v>50.61</v>
       </c>
       <c r="F58">
-        <v>9.49</v>
+        <v>11.27</v>
       </c>
       <c r="G58">
-        <v>3.76</v>
+        <v>3.69</v>
       </c>
       <c r="H58">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="I58">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="J58">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -2979,28 +2979,28 @@
         <v>69</v>
       </c>
       <c r="C59">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D59" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E59">
-        <v>72.45999999999999</v>
+        <v>49.39</v>
       </c>
       <c r="F59">
-        <v>18.33</v>
+        <v>10.75</v>
       </c>
       <c r="G59">
-        <v>5.63</v>
+        <v>3.46</v>
       </c>
       <c r="H59">
-        <v>1.64</v>
+        <v>1.16</v>
       </c>
       <c r="I59">
-        <v>0.42</v>
+        <v>0.12</v>
       </c>
       <c r="J59">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -3014,25 +3014,25 @@
         <v>70</v>
       </c>
       <c r="C60">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E60">
-        <v>57.76</v>
+        <v>72.41</v>
       </c>
       <c r="F60">
-        <v>16.55</v>
+        <v>18.35</v>
       </c>
       <c r="G60">
-        <v>5.23</v>
+        <v>5.66</v>
       </c>
       <c r="H60">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="I60">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="J60">
         <v>0.04</v>
@@ -3052,31 +3052,31 @@
         <v>92</v>
       </c>
       <c r="D61" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E61">
-        <v>67.66</v>
+        <v>67.7</v>
       </c>
       <c r="F61">
-        <v>23.07</v>
+        <v>23.19</v>
       </c>
       <c r="G61">
-        <v>4.71</v>
+        <v>4.78</v>
       </c>
       <c r="H61">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="I61">
         <v>0.44</v>
       </c>
       <c r="J61">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="K61">
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3084,34 +3084,34 @@
         <v>72</v>
       </c>
       <c r="C62">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D62" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E62">
-        <v>48.58</v>
+        <v>57.12</v>
       </c>
       <c r="F62">
-        <v>7.67</v>
+        <v>21.42</v>
       </c>
       <c r="G62">
-        <v>3.29</v>
+        <v>5.72</v>
       </c>
       <c r="H62">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="I62">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="J62">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3119,25 +3119,25 @@
         <v>73</v>
       </c>
       <c r="C63">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E63">
-        <v>54.3</v>
+        <v>44.33</v>
       </c>
       <c r="F63">
-        <v>12.11</v>
+        <v>11.7</v>
       </c>
       <c r="G63">
-        <v>3.54</v>
+        <v>4.04</v>
       </c>
       <c r="H63">
-        <v>0.97</v>
+        <v>0.32</v>
       </c>
       <c r="I63">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="J63">
         <v>0.02</v>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3154,25 +3154,25 @@
         <v>74</v>
       </c>
       <c r="C64">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E64">
-        <v>62.13</v>
+        <v>48.56</v>
       </c>
       <c r="F64">
-        <v>13</v>
+        <v>7.66</v>
       </c>
       <c r="G64">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="H64">
-        <v>0.8100000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="I64">
-        <v>0.07000000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="J64">
         <v>0.02</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="L64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3189,25 +3189,25 @@
         <v>75</v>
       </c>
       <c r="C65">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D65" t="s">
         <v>112</v>
       </c>
       <c r="E65">
-        <v>57.01</v>
+        <v>41.55</v>
       </c>
       <c r="F65">
-        <v>21.39</v>
+        <v>11.43</v>
       </c>
       <c r="G65">
-        <v>5.76</v>
+        <v>4.13</v>
       </c>
       <c r="H65">
-        <v>1.32</v>
+        <v>0.97</v>
       </c>
       <c r="I65">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="J65">
         <v>0.02</v>
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="L65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3224,25 +3224,25 @@
         <v>76</v>
       </c>
       <c r="C66">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D66" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E66">
-        <v>41.52</v>
+        <v>54.3</v>
       </c>
       <c r="F66">
-        <v>11.45</v>
+        <v>12.11</v>
       </c>
       <c r="G66">
-        <v>4.13</v>
+        <v>3.52</v>
       </c>
       <c r="H66">
         <v>0.96</v>
       </c>
       <c r="I66">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J66">
         <v>0.02</v>
@@ -3259,25 +3259,25 @@
         <v>77</v>
       </c>
       <c r="C67">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="D67" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E67">
-        <v>57.1</v>
+        <v>62</v>
       </c>
       <c r="F67">
-        <v>19.18</v>
+        <v>12.96</v>
       </c>
       <c r="G67">
-        <v>4.08</v>
+        <v>2.96</v>
       </c>
       <c r="H67">
-        <v>1.34</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I67">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J67">
         <v>0.02</v>
@@ -3294,34 +3294,34 @@
         <v>78</v>
       </c>
       <c r="C68">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E68">
-        <v>59.9</v>
+        <v>41.55</v>
       </c>
       <c r="F68">
-        <v>12.79</v>
+        <v>9.09</v>
       </c>
       <c r="G68">
-        <v>3.87</v>
+        <v>4.09</v>
       </c>
       <c r="H68">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="I68">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J68">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3329,34 +3329,34 @@
         <v>79</v>
       </c>
       <c r="C69">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>
       </c>
       <c r="E69">
-        <v>50.04</v>
+        <v>57.1</v>
       </c>
       <c r="F69">
-        <v>18.75</v>
+        <v>19.14</v>
       </c>
       <c r="G69">
-        <v>4.78</v>
+        <v>4.06</v>
       </c>
       <c r="H69">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="I69">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="J69">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3364,25 +3364,25 @@
         <v>80</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="D70" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E70">
-        <v>37.42</v>
+        <v>33.61</v>
       </c>
       <c r="F70">
-        <v>1.34</v>
+        <v>4.72</v>
       </c>
       <c r="G70">
-        <v>0.57</v>
+        <v>1.75</v>
       </c>
       <c r="H70">
-        <v>0.19</v>
+        <v>0.55</v>
       </c>
       <c r="I70">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="J70">
         <v>0.01</v>
@@ -3399,25 +3399,25 @@
         <v>81</v>
       </c>
       <c r="C71">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="D71" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E71">
-        <v>44.32</v>
+        <v>59.89</v>
       </c>
       <c r="F71">
-        <v>11.71</v>
+        <v>12.78</v>
       </c>
       <c r="G71">
-        <v>4.06</v>
+        <v>3.88</v>
       </c>
       <c r="H71">
-        <v>0.33</v>
+        <v>0.97</v>
       </c>
       <c r="I71">
-        <v>0.08</v>
+        <v>0.22</v>
       </c>
       <c r="J71">
         <v>0.02</v>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="L71" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3434,25 +3434,25 @@
         <v>82</v>
       </c>
       <c r="C72">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E72">
-        <v>33.61</v>
+        <v>50</v>
       </c>
       <c r="F72">
-        <v>4.74</v>
+        <v>18.74</v>
       </c>
       <c r="G72">
-        <v>1.76</v>
+        <v>4.79</v>
       </c>
       <c r="H72">
-        <v>0.5600000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="I72">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J72">
         <v>0.01</v>
@@ -3461,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="L72" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3469,25 +3469,25 @@
         <v>83</v>
       </c>
       <c r="C73">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="D73" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E73">
-        <v>22.79</v>
+        <v>42.34</v>
       </c>
       <c r="F73">
-        <v>4.34</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G73">
-        <v>1.73</v>
+        <v>2.49</v>
       </c>
       <c r="H73">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="I73">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="J73">
         <v>0.01</v>
@@ -3504,25 +3504,25 @@
         <v>84</v>
       </c>
       <c r="C74">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s">
         <v>109</v>
       </c>
       <c r="E74">
-        <v>41.58</v>
+        <v>52.89</v>
       </c>
       <c r="F74">
-        <v>9.029999999999999</v>
+        <v>11.53</v>
       </c>
       <c r="G74">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="I74">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J74">
         <v>0.01</v>
@@ -3539,25 +3539,25 @@
         <v>85</v>
       </c>
       <c r="C75">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D75" t="s">
         <v>111</v>
       </c>
       <c r="E75">
-        <v>42.24</v>
+        <v>54.89</v>
       </c>
       <c r="F75">
-        <v>9.59</v>
+        <v>7.39</v>
       </c>
       <c r="G75">
-        <v>2.49</v>
+        <v>2.16</v>
       </c>
       <c r="H75">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="I75">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="J75">
         <v>0.01</v>
@@ -3574,25 +3574,25 @@
         <v>86</v>
       </c>
       <c r="C76">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D76" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E76">
-        <v>42.9</v>
+        <v>45.7</v>
       </c>
       <c r="F76">
-        <v>11.85</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G76">
-        <v>1.99</v>
+        <v>2.33</v>
       </c>
       <c r="H76">
         <v>0.55</v>
       </c>
       <c r="I76">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="J76">
         <v>0.01</v>
@@ -3601,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3609,25 +3609,25 @@
         <v>87</v>
       </c>
       <c r="C77">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E77">
-        <v>28.18</v>
+        <v>37.49</v>
       </c>
       <c r="F77">
-        <v>10.18</v>
+        <v>1.32</v>
       </c>
       <c r="G77">
-        <v>1.64</v>
+        <v>0.57</v>
       </c>
       <c r="H77">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="I77">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="J77">
         <v>0.01</v>
@@ -3636,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="L77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3644,25 +3644,25 @@
         <v>88</v>
       </c>
       <c r="C78">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E78">
-        <v>42.99</v>
+        <v>47.11</v>
       </c>
       <c r="F78">
-        <v>13.34</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G78">
-        <v>2.91</v>
+        <v>3.09</v>
       </c>
       <c r="H78">
-        <v>0.55</v>
+        <v>0.18</v>
       </c>
       <c r="I78">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="J78">
         <v>0.01</v>
@@ -3679,25 +3679,25 @@
         <v>89</v>
       </c>
       <c r="C79">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D79" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E79">
-        <v>55.02</v>
+        <v>50</v>
       </c>
       <c r="F79">
-        <v>7.35</v>
+        <v>18.71</v>
       </c>
       <c r="G79">
-        <v>2.15</v>
+        <v>4.78</v>
       </c>
       <c r="H79">
-        <v>0.42</v>
+        <v>1.07</v>
       </c>
       <c r="I79">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J79">
         <v>0.01</v>
@@ -3714,25 +3714,25 @@
         <v>90</v>
       </c>
       <c r="C80">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D80" t="s">
         <v>109</v>
       </c>
       <c r="E80">
-        <v>49.96</v>
+        <v>22.7</v>
       </c>
       <c r="F80">
-        <v>18.72</v>
+        <v>4.34</v>
       </c>
       <c r="G80">
-        <v>4.77</v>
+        <v>1.74</v>
       </c>
       <c r="H80">
-        <v>1.08</v>
+        <v>0.59</v>
       </c>
       <c r="I80">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="J80">
         <v>0.01</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3749,34 +3749,34 @@
         <v>91</v>
       </c>
       <c r="C81">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D81" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E81">
-        <v>32.23</v>
+        <v>42.88</v>
       </c>
       <c r="F81">
-        <v>5.45</v>
+        <v>13.3</v>
       </c>
       <c r="G81">
-        <v>1.95</v>
+        <v>2.92</v>
       </c>
       <c r="H81">
-        <v>0.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I81">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K81">
         <v>0</v>
       </c>
       <c r="L81" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3784,34 +3784,34 @@
         <v>92</v>
       </c>
       <c r="C82">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D82" t="s">
         <v>109</v>
       </c>
       <c r="E82">
-        <v>52.88</v>
+        <v>42.9</v>
       </c>
       <c r="F82">
-        <v>11.56</v>
+        <v>11.86</v>
       </c>
       <c r="G82">
-        <v>4.09</v>
+        <v>2.01</v>
       </c>
       <c r="H82">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="I82">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="J82">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K82">
         <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3819,28 +3819,28 @@
         <v>93</v>
       </c>
       <c r="C83">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="D83" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E83">
-        <v>45.7</v>
+        <v>35.47</v>
       </c>
       <c r="F83">
-        <v>8.859999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="G83">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="H83">
-        <v>0.55</v>
+        <v>0.13</v>
       </c>
       <c r="I83">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="J83">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K83">
         <v>0</v>
@@ -3854,25 +3854,25 @@
         <v>94</v>
       </c>
       <c r="C84">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D84" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E84">
-        <v>33.56</v>
+        <v>32.94</v>
       </c>
       <c r="F84">
-        <v>6.87</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G84">
-        <v>1.09</v>
+        <v>0.35</v>
       </c>
       <c r="H84">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="I84">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -3889,34 +3889,34 @@
         <v>95</v>
       </c>
       <c r="C85">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D85" t="s">
         <v>111</v>
       </c>
       <c r="E85">
-        <v>40.1</v>
+        <v>28.09</v>
       </c>
       <c r="F85">
-        <v>6.17</v>
+        <v>10.16</v>
       </c>
       <c r="G85">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="H85">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="I85">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K85">
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -3924,34 +3924,34 @@
         <v>96</v>
       </c>
       <c r="C86">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D86" t="s">
         <v>110</v>
       </c>
       <c r="E86">
-        <v>66.36</v>
+        <v>31.63</v>
       </c>
       <c r="F86">
-        <v>2.1</v>
+        <v>5.13</v>
       </c>
       <c r="G86">
-        <v>0.61</v>
+        <v>1.35</v>
       </c>
       <c r="H86">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="I86">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="J86">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K86">
         <v>0</v>
       </c>
       <c r="L86" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -3959,34 +3959,34 @@
         <v>97</v>
       </c>
       <c r="C87">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="D87" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E87">
-        <v>32.98</v>
+        <v>66.52</v>
       </c>
       <c r="F87">
-        <v>9.5</v>
+        <v>2.1</v>
       </c>
       <c r="G87">
-        <v>0.36</v>
+        <v>0.61</v>
       </c>
       <c r="H87">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I87">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K87">
         <v>0</v>
       </c>
       <c r="L87" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -3994,25 +3994,25 @@
         <v>98</v>
       </c>
       <c r="C88">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D88" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E88">
-        <v>35.42</v>
+        <v>32.3</v>
       </c>
       <c r="F88">
-        <v>9.949999999999999</v>
+        <v>5.48</v>
       </c>
       <c r="G88">
-        <v>2.53</v>
+        <v>1.96</v>
       </c>
       <c r="H88">
-        <v>0.13</v>
+        <v>0.37</v>
       </c>
       <c r="I88">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4029,28 +4029,28 @@
         <v>99</v>
       </c>
       <c r="C89">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="D89" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E89">
-        <v>47.12</v>
+        <v>33.53</v>
       </c>
       <c r="F89">
-        <v>9.369999999999999</v>
+        <v>6.83</v>
       </c>
       <c r="G89">
-        <v>3.08</v>
+        <v>1.09</v>
       </c>
       <c r="H89">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="I89">
         <v>0.03</v>
       </c>
       <c r="J89">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K89">
         <v>0</v>
@@ -4064,25 +4064,25 @@
         <v>100</v>
       </c>
       <c r="C90">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D90" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E90">
-        <v>22.24</v>
+        <v>45.11</v>
       </c>
       <c r="F90">
-        <v>3.66</v>
+        <v>5.12</v>
       </c>
       <c r="G90">
-        <v>0.44</v>
+        <v>1.31</v>
       </c>
       <c r="H90">
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
       <c r="I90">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -4099,25 +4099,25 @@
         <v>101</v>
       </c>
       <c r="C91">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D91" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E91">
-        <v>27.54</v>
+        <v>32.3</v>
       </c>
       <c r="F91">
-        <v>3.19</v>
+        <v>6.44</v>
       </c>
       <c r="G91">
-        <v>0.48</v>
+        <v>0.75</v>
       </c>
       <c r="H91">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="I91">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -4134,25 +4134,25 @@
         <v>102</v>
       </c>
       <c r="C92">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="D92" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E92">
-        <v>32.34</v>
+        <v>33.48</v>
       </c>
       <c r="F92">
-        <v>6.42</v>
+        <v>0.61</v>
       </c>
       <c r="G92">
-        <v>0.74</v>
+        <v>0.11</v>
       </c>
       <c r="H92">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="I92">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -4169,25 +4169,25 @@
         <v>103</v>
       </c>
       <c r="C93">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E93">
-        <v>37.87</v>
+        <v>0</v>
       </c>
       <c r="F93">
-        <v>5.31</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="I93">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -4196,15 +4196,15 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D94" t="s">
         <v>109</v>
@@ -4236,10 +4236,10 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D95" t="s">
         <v>109</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C96">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D96" t="s">
         <v>109</v>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C97">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D97" t="s">
         <v>109</v>
@@ -4341,10 +4341,10 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C98">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D98" t="s">
         <v>109</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C99">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D99" t="s">
         <v>109</v>
@@ -4411,10 +4411,10 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C100">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D100" t="s">
         <v>109</v>
@@ -4446,13 +4446,13 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C101">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D101" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -4481,13 +4481,13 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C102">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D102" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -4516,13 +4516,13 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C103">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D103" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4551,13 +4551,13 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C104">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D104" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4586,13 +4586,13 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C105">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D105" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -4621,13 +4621,13 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C106">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D106" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -4656,13 +4656,13 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C107">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D107" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -4694,25 +4694,25 @@
         <v>104</v>
       </c>
       <c r="C108">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D108" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>22.19</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I108">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -4726,28 +4726,28 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C109">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D109" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E109">
-        <v>44.98</v>
+        <v>0</v>
       </c>
       <c r="F109">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="G109">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="I109">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C110">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D110" t="s">
         <v>112</v>
@@ -4796,28 +4796,28 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C111">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D111" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>27.59</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I111">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -4831,13 +4831,13 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C112">
         <v>71</v>
       </c>
       <c r="D112" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -4866,13 +4866,13 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C113">
         <v>74</v>
       </c>
       <c r="D113" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -4901,28 +4901,28 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C114">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D114" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>40.11</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="I114">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -4936,13 +4936,13 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C115">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D115" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4971,28 +4971,28 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C116">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D116" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E116">
-        <v>24.27</v>
+        <v>0</v>
       </c>
       <c r="F116">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="G116">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="H116">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="I116">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -5006,28 +5006,28 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C117">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D117" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>24.29</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="I117">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -5041,13 +5041,13 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C118">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D118" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -5076,13 +5076,13 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C119">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D119" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -5111,13 +5111,13 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C120">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D120" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -5146,10 +5146,10 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C121">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D121" t="s">
         <v>110</v>
@@ -5181,28 +5181,28 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C122">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D122" t="s">
         <v>110</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="I122">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -5216,28 +5216,28 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C123">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D123" t="s">
         <v>110</v>
       </c>
       <c r="E123">
-        <v>31.68</v>
+        <v>0</v>
       </c>
       <c r="F123">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="I123">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C124">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D124" t="s">
         <v>110</v>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C125">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D125" t="s">
         <v>110</v>
@@ -5321,10 +5321,10 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C126">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D126" t="s">
         <v>110</v>
@@ -5356,10 +5356,10 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C127">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D127" t="s">
         <v>110</v>
@@ -5391,25 +5391,25 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C128">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D128" t="s">
         <v>110</v>
       </c>
       <c r="E128">
-        <v>33.64</v>
+        <v>0</v>
       </c>
       <c r="F128">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="G128">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -5426,7 +5426,7 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C129">
         <v>127</v>

--- a/sim-output/IndianWells-2026_results.xlsx
+++ b/sim-output/IndianWells-2026_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="193">
   <si>
     <t>Player</t>
   </si>
@@ -79,15 +79,15 @@
     <t>Jack Draper</t>
   </si>
   <si>
+    <t>Felix Auger Aliassime</t>
+  </si>
+  <si>
     <t>Jakub Mensik</t>
   </si>
   <si>
     <t>Learner Tien</t>
   </si>
   <si>
-    <t>Felix Auger Aliassime</t>
-  </si>
-  <si>
     <t>Lorenzo Musetti</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Jiri Lehecka</t>
   </si>
   <si>
+    <t>Flavio Cobolli</t>
+  </si>
+  <si>
     <t>Alejandro Davidovich Fokina</t>
   </si>
   <si>
-    <t>Flavio Cobolli</t>
-  </si>
-  <si>
     <t>Brandon Nakashima</t>
   </si>
   <si>
@@ -139,12 +139,12 @@
     <t>Joao Fonseca</t>
   </si>
   <si>
+    <t>Francisco Cerundolo</t>
+  </si>
+  <si>
     <t>Hubert Hurkacz</t>
   </si>
   <si>
-    <t>Francisco Cerundolo</t>
-  </si>
-  <si>
     <t>Matteo Berrettini</t>
   </si>
   <si>
@@ -157,6 +157,9 @@
     <t>Miomir Kecmanovic</t>
   </si>
   <si>
+    <t>Alex Michelsen</t>
+  </si>
+  <si>
     <t>Luciano Darderi</t>
   </si>
   <si>
@@ -166,18 +169,15 @@
     <t>Denis Shapovalov</t>
   </si>
   <si>
-    <t>Alex Michelsen</t>
+    <t>Corentin Moutet</t>
+  </si>
+  <si>
+    <t>Tomas Martin Etcheverry</t>
   </si>
   <si>
     <t>Grigor Dimitrov</t>
   </si>
   <si>
-    <t>Corentin Moutet</t>
-  </si>
-  <si>
-    <t>Tomas Martin Etcheverry</t>
-  </si>
-  <si>
     <t>Marin Cilic</t>
   </si>
   <si>
@@ -187,15 +187,15 @@
     <t>Jenson Brooksby</t>
   </si>
   <si>
+    <t>Rafael Jodar</t>
+  </si>
+  <si>
+    <t>Raphael Collignon</t>
+  </si>
+  <si>
     <t>Nuno Borges</t>
   </si>
   <si>
-    <t>Raphael Collignon</t>
-  </si>
-  <si>
-    <t>Rafael Jodar</t>
-  </si>
-  <si>
     <t>Botic Van De Zandschulp</t>
   </si>
   <si>
@@ -214,135 +214,135 @@
     <t>Alejandro Tabilo</t>
   </si>
   <si>
+    <t>Martin Damm</t>
+  </si>
+  <si>
+    <t>Gabriel Diallo</t>
+  </si>
+  <si>
+    <t>Reilly Opelka</t>
+  </si>
+  <si>
     <t>Kamil Majchrzak</t>
   </si>
   <si>
-    <t>Gabriel Diallo</t>
-  </si>
-  <si>
-    <t>Reilly Opelka</t>
-  </si>
-  <si>
     <t>Ethan Quinn</t>
   </si>
   <si>
+    <t>Giovanni Mpetshi Perricard</t>
+  </si>
+  <si>
     <t>Dino Prizmic</t>
   </si>
   <si>
-    <t>Martin Damm</t>
-  </si>
-  <si>
     <t>Benjamin Bonzi</t>
   </si>
   <si>
+    <t>Marton Fucsovics</t>
+  </si>
+  <si>
+    <t>Alexei Popyrin</t>
+  </si>
+  <si>
+    <t>Mackenzie Mcdonald</t>
+  </si>
+  <si>
+    <t>Rinky Hijikata</t>
+  </si>
+  <si>
     <t>Jan Lennard Struff</t>
   </si>
   <si>
-    <t>Giovanni Mpetshi Perricard</t>
-  </si>
-  <si>
-    <t>Alexei Popyrin</t>
-  </si>
-  <si>
-    <t>Marton Fucsovics</t>
-  </si>
-  <si>
     <t>Quentin Halys</t>
   </si>
   <si>
     <t>Arthur Cazaux</t>
   </si>
   <si>
-    <t>Mackenzie Mcdonald</t>
+    <t>Gael Monfils</t>
   </si>
   <si>
     <t>Adrian Mannarino</t>
   </si>
   <si>
-    <t>Gael Monfils</t>
+    <t>Terence Atmane</t>
   </si>
   <si>
     <t>Francesco Maestrelli</t>
   </si>
   <si>
+    <t>Francisco Comesana</t>
+  </si>
+  <si>
     <t>Mattia Bellucci</t>
   </si>
   <si>
     <t>Sho Shimabukuro</t>
   </si>
   <si>
+    <t>Emilio Nava</t>
+  </si>
+  <si>
+    <t>Valentin Royer</t>
+  </si>
+  <si>
+    <t>Christopher Oconnell</t>
+  </si>
+  <si>
+    <t>Matteo Arnaldi</t>
+  </si>
+  <si>
+    <t>Aleksandar Kovacevic</t>
+  </si>
+  <si>
+    <t>Roberto Bautista Agut</t>
+  </si>
+  <si>
+    <t>Chun Hsin Tseng</t>
+  </si>
+  <si>
     <t>Jacob Fearnley</t>
   </si>
   <si>
-    <t>Christopher Oconnell</t>
-  </si>
-  <si>
-    <t>Terence Atmane</t>
+    <t>Alexis Galarneau</t>
   </si>
   <si>
     <t>Alexander Shevchenko</t>
   </si>
   <si>
-    <t>Rinky Hijikata</t>
-  </si>
-  <si>
-    <t>Francisco Comesana</t>
-  </si>
-  <si>
-    <t>Valentin Royer</t>
-  </si>
-  <si>
-    <t>Matteo Arnaldi</t>
-  </si>
-  <si>
-    <t>Emilio Nava</t>
+    <t>Damir Dzumhur</t>
+  </si>
+  <si>
+    <t>Daniel Altmaier</t>
+  </si>
+  <si>
+    <t>Mariano Navone</t>
+  </si>
+  <si>
+    <t>Dalibor Svrcina</t>
+  </si>
+  <si>
+    <t>Tristan Schoolkate</t>
+  </si>
+  <si>
+    <t>Bye</t>
   </si>
   <si>
     <t>Juan Manuel Cerundolo</t>
   </si>
   <si>
-    <t>Aleksandar Kovacevic</t>
-  </si>
-  <si>
-    <t>Mariano Navone</t>
-  </si>
-  <si>
-    <t>Dalibor Svrcina</t>
-  </si>
-  <si>
-    <t>Roberto Bautista Agut</t>
-  </si>
-  <si>
-    <t>Chun Hsin Tseng</t>
-  </si>
-  <si>
-    <t>Damir Dzumhur</t>
+    <t>Daniel Merida Aguilar</t>
   </si>
   <si>
     <t>Camilo Ugo Carabelli</t>
   </si>
   <si>
+    <t>Adam Walton</t>
+  </si>
+  <si>
     <t>James Duckworth</t>
   </si>
   <si>
-    <t>Bye</t>
-  </si>
-  <si>
-    <t>Daniel Merida Aguilar</t>
-  </si>
-  <si>
-    <t>Tristan Schoolkate</t>
-  </si>
-  <si>
-    <t>Alexis Galarneau</t>
-  </si>
-  <si>
-    <t>Daniel Altmaier</t>
-  </si>
-  <si>
-    <t>Adam Walton</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
@@ -355,205 +355,217 @@
     <t>Q3</t>
   </si>
   <si>
-    <t>+121</t>
-  </si>
-  <si>
-    <t>+174</t>
-  </si>
-  <si>
-    <t>+3419</t>
-  </si>
-  <si>
-    <t>+3428</t>
-  </si>
-  <si>
-    <t>+5476</t>
-  </si>
-  <si>
-    <t>+6010</t>
-  </si>
-  <si>
-    <t>+8765</t>
-  </si>
-  <si>
-    <t>+12616</t>
-  </si>
-  <si>
-    <t>+13080</t>
-  </si>
-  <si>
-    <t>+15668</t>
-  </si>
-  <si>
-    <t>+15869</t>
-  </si>
-  <si>
-    <t>+15967</t>
-  </si>
-  <si>
-    <t>+16597</t>
-  </si>
-  <si>
-    <t>+19698</t>
-  </si>
-  <si>
-    <t>+20651</t>
-  </si>
-  <si>
-    <t>+27267</t>
-  </si>
-  <si>
-    <t>+29200</t>
-  </si>
-  <si>
-    <t>+29644</t>
-  </si>
-  <si>
-    <t>+34182</t>
-  </si>
-  <si>
-    <t>+39208</t>
-  </si>
-  <si>
-    <t>+50946</t>
-  </si>
-  <si>
-    <t>+74638</t>
-  </si>
-  <si>
-    <t>+78578</t>
-  </si>
-  <si>
-    <t>+80221</t>
-  </si>
-  <si>
-    <t>+81069</t>
-  </si>
-  <si>
-    <t>+115107</t>
-  </si>
-  <si>
-    <t>+138982</t>
-  </si>
-  <si>
-    <t>+169679</t>
-  </si>
-  <si>
-    <t>+178791</t>
-  </si>
-  <si>
-    <t>+203152</t>
-  </si>
-  <si>
-    <t>+203982</t>
-  </si>
-  <si>
-    <t>+254353</t>
-  </si>
-  <si>
-    <t>+332126</t>
-  </si>
-  <si>
-    <t>+378688</t>
-  </si>
-  <si>
-    <t>+381579</t>
-  </si>
-  <si>
-    <t>+482992</t>
-  </si>
-  <si>
-    <t>+512721</t>
-  </si>
-  <si>
-    <t>+571329</t>
-  </si>
-  <si>
-    <t>+602310</t>
+    <t>+136</t>
+  </si>
+  <si>
+    <t>+184</t>
+  </si>
+  <si>
+    <t>+2766</t>
+  </si>
+  <si>
+    <t>+2795</t>
+  </si>
+  <si>
+    <t>+4541</t>
+  </si>
+  <si>
+    <t>+4958</t>
+  </si>
+  <si>
+    <t>+7092</t>
+  </si>
+  <si>
+    <t>+10217</t>
+  </si>
+  <si>
+    <t>+10698</t>
+  </si>
+  <si>
+    <t>+12545</t>
+  </si>
+  <si>
+    <t>+12795</t>
+  </si>
+  <si>
+    <t>+12835</t>
+  </si>
+  <si>
+    <t>+13642</t>
+  </si>
+  <si>
+    <t>+16073</t>
+  </si>
+  <si>
+    <t>+16310</t>
+  </si>
+  <si>
+    <t>+22443</t>
+  </si>
+  <si>
+    <t>+24500</t>
+  </si>
+  <si>
+    <t>+24831</t>
+  </si>
+  <si>
+    <t>+28512</t>
+  </si>
+  <si>
+    <t>+31307</t>
+  </si>
+  <si>
+    <t>+40550</t>
+  </si>
+  <si>
+    <t>+59960</t>
+  </si>
+  <si>
+    <t>+60616</t>
+  </si>
+  <si>
+    <t>+65863</t>
+  </si>
+  <si>
+    <t>+69538</t>
+  </si>
+  <si>
+    <t>+92321</t>
+  </si>
+  <si>
+    <t>+122750</t>
+  </si>
+  <si>
+    <t>+134853</t>
+  </si>
+  <si>
+    <t>+137074</t>
+  </si>
+  <si>
+    <t>+161451</t>
+  </si>
+  <si>
+    <t>+169968</t>
+  </si>
+  <si>
+    <t>+232458</t>
+  </si>
+  <si>
+    <t>+246814</t>
+  </si>
+  <si>
+    <t>+272380</t>
+  </si>
+  <si>
+    <t>+299301</t>
+  </si>
+  <si>
+    <t>+375840</t>
+  </si>
+  <si>
+    <t>+380128</t>
+  </si>
+  <si>
+    <t>+413123</t>
+  </si>
+  <si>
+    <t>+427250</t>
+  </si>
+  <si>
+    <t>+480669</t>
+  </si>
+  <si>
+    <t>+534659</t>
+  </si>
+  <si>
+    <t>+546348</t>
+  </si>
+  <si>
+    <t>+584695</t>
   </si>
   <si>
     <t>+609656</t>
   </si>
   <si>
-    <t>+694344</t>
-  </si>
-  <si>
-    <t>+704125</t>
-  </si>
-  <si>
-    <t>+757476</t>
-  </si>
-  <si>
-    <t>+775094</t>
-  </si>
-  <si>
-    <t>+999900</t>
-  </si>
-  <si>
-    <t>+1204719</t>
-  </si>
-  <si>
-    <t>+1234468</t>
-  </si>
-  <si>
-    <t>+1265723</t>
+    <t>+671041</t>
+  </si>
+  <si>
+    <t>+793551</t>
+  </si>
+  <si>
+    <t>+877093</t>
+  </si>
+  <si>
+    <t>+934479</t>
+  </si>
+  <si>
+    <t>+1030828</t>
+  </si>
+  <si>
+    <t>+1098801</t>
+  </si>
+  <si>
+    <t>+1249900</t>
+  </si>
+  <si>
+    <t>+1315689</t>
   </si>
   <si>
     <t>+1562400</t>
   </si>
   <si>
-    <t>+1639244</t>
+    <t>+1587202</t>
   </si>
   <si>
     <t>+1666567</t>
   </si>
   <si>
-    <t>+1724038</t>
-  </si>
-  <si>
-    <t>+2173813</t>
-  </si>
-  <si>
-    <t>+2438924</t>
+    <t>+1922977</t>
+  </si>
+  <si>
+    <t>+1960684</t>
+  </si>
+  <si>
+    <t>+1999900</t>
+  </si>
+  <si>
+    <t>+2222122</t>
+  </si>
+  <si>
+    <t>+2325481</t>
   </si>
   <si>
     <t>+2631479</t>
   </si>
   <si>
-    <t>+2857043</t>
-  </si>
-  <si>
-    <t>+3030203</t>
-  </si>
-  <si>
-    <t>+3124900</t>
+    <t>+2702603</t>
   </si>
   <si>
     <t>+3448176</t>
   </si>
   <si>
-    <t>+3571329</t>
-  </si>
-  <si>
-    <t>+3846054</t>
+    <t>+3703604</t>
+  </si>
+  <si>
+    <t>+4545355</t>
   </si>
   <si>
     <t>+4999900</t>
   </si>
   <si>
+    <t>+5263058</t>
+  </si>
+  <si>
     <t>+5882253</t>
   </si>
   <si>
-    <t>+6249900</t>
+    <t>+6666567</t>
   </si>
   <si>
     <t>+7142757</t>
   </si>
   <si>
-    <t>+7692208</t>
-  </si>
-  <si>
-    <t>+9090809</t>
+    <t>+8333233</t>
   </si>
   <si>
     <t>+9999900</t>
@@ -565,13 +577,13 @@
     <t>+14285614</t>
   </si>
   <si>
+    <t>+16666567</t>
+  </si>
+  <si>
     <t>+19999900</t>
   </si>
   <si>
     <t>+24999900</t>
-  </si>
-  <si>
-    <t>+33333233</t>
   </si>
   <si>
     <t>+49999900</t>
@@ -993,22 +1005,22 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>95.23999999999999</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="G2">
-        <v>90.72</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H2">
-        <v>84.44</v>
+        <v>82.16</v>
       </c>
       <c r="I2">
-        <v>77.09999999999999</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="J2">
-        <v>66.95</v>
+        <v>62.7</v>
       </c>
       <c r="K2">
-        <v>45.16</v>
+        <v>42.41</v>
       </c>
       <c r="L2" t="s">
         <v>113</v>
@@ -1028,22 +1040,22 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>97.29000000000001</v>
+        <v>96.97</v>
       </c>
       <c r="G3">
-        <v>90.7</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="H3">
-        <v>82.37</v>
+        <v>80.3</v>
       </c>
       <c r="I3">
-        <v>71.92</v>
+        <v>68.84</v>
       </c>
       <c r="J3">
-        <v>62.68</v>
+        <v>58.84</v>
       </c>
       <c r="K3">
-        <v>36.52</v>
+        <v>35.18</v>
       </c>
       <c r="L3" t="s">
         <v>114</v>
@@ -1063,22 +1075,22 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>83.78</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="G4">
-        <v>66.91</v>
+        <v>67.03</v>
       </c>
       <c r="H4">
-        <v>47.14</v>
+        <v>47.18</v>
       </c>
       <c r="I4">
-        <v>28.23</v>
+        <v>28.29</v>
       </c>
       <c r="J4">
-        <v>8.039999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="K4">
-        <v>2.84</v>
+        <v>3.49</v>
       </c>
       <c r="L4" t="s">
         <v>115</v>
@@ -1098,22 +1110,22 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>79.13</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="G5">
-        <v>61.43</v>
+        <v>61.5</v>
       </c>
       <c r="H5">
-        <v>45.29</v>
+        <v>45.27</v>
       </c>
       <c r="I5">
-        <v>30.06</v>
+        <v>30.08</v>
       </c>
       <c r="J5">
-        <v>9.460000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="K5">
-        <v>2.83</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="s">
         <v>116</v>
@@ -1133,22 +1145,22 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>87.48</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="G6">
-        <v>63.11</v>
+        <v>63.09</v>
       </c>
       <c r="H6">
-        <v>37.05</v>
+        <v>37.07</v>
       </c>
       <c r="I6">
-        <v>21.16</v>
+        <v>21.18</v>
       </c>
       <c r="J6">
-        <v>5.5</v>
+        <v>6.18</v>
       </c>
       <c r="K6">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="L6" t="s">
         <v>117</v>
@@ -1168,10 +1180,10 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>78.37</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G7">
-        <v>55.55</v>
+        <v>55.56</v>
       </c>
       <c r="H7">
         <v>32.82</v>
@@ -1180,10 +1192,10 @@
         <v>18.94</v>
       </c>
       <c r="J7">
-        <v>4.98</v>
+        <v>5.59</v>
       </c>
       <c r="K7">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="L7" t="s">
         <v>118</v>
@@ -1203,22 +1215,22 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>77.98</v>
+        <v>78.05</v>
       </c>
       <c r="G8">
-        <v>47.48</v>
+        <v>47.5</v>
       </c>
       <c r="H8">
-        <v>30.03</v>
+        <v>30.06</v>
       </c>
       <c r="I8">
-        <v>7.41</v>
+        <v>8.23</v>
       </c>
       <c r="J8">
-        <v>4.24</v>
+        <v>4.72</v>
       </c>
       <c r="K8">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="L8" t="s">
         <v>119</v>
@@ -1238,22 +1250,22 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>61.4</v>
+        <v>61.53</v>
       </c>
       <c r="G9">
-        <v>44.97</v>
+        <v>45.07</v>
       </c>
       <c r="H9">
-        <v>29.71</v>
+        <v>29.82</v>
       </c>
       <c r="I9">
-        <v>5.92</v>
+        <v>6.73</v>
       </c>
       <c r="J9">
-        <v>2.83</v>
+        <v>3.19</v>
       </c>
       <c r="K9">
-        <v>0.79</v>
+        <v>0.97</v>
       </c>
       <c r="L9" t="s">
         <v>120</v>
@@ -1273,22 +1285,22 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>74.33</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="G10">
-        <v>54.18</v>
+        <v>54.14</v>
       </c>
       <c r="H10">
-        <v>26.69</v>
+        <v>26.62</v>
       </c>
       <c r="I10">
-        <v>12.95</v>
+        <v>12.9</v>
       </c>
       <c r="J10">
-        <v>2.82</v>
+        <v>3.14</v>
       </c>
       <c r="K10">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="L10" t="s">
         <v>121</v>
@@ -1299,31 +1311,31 @@
         <v>21</v>
       </c>
       <c r="C11">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
         <v>112</v>
-      </c>
-      <c r="D11" t="s">
-        <v>110</v>
       </c>
       <c r="E11">
         <v>100</v>
       </c>
       <c r="F11">
-        <v>74.92</v>
+        <v>80.98</v>
       </c>
       <c r="G11">
-        <v>48.28</v>
+        <v>48.7</v>
       </c>
       <c r="H11">
-        <v>24.2</v>
+        <v>26.27</v>
       </c>
       <c r="I11">
-        <v>5.24</v>
+        <v>13.22</v>
       </c>
       <c r="J11">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="K11">
-        <v>0.63</v>
+        <v>0.79</v>
       </c>
       <c r="L11" t="s">
         <v>122</v>
@@ -1334,7 +1346,7 @@
         <v>22</v>
       </c>
       <c r="C12">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
         <v>110</v>
@@ -1343,22 +1355,22 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>81.73</v>
+        <v>74.88</v>
       </c>
       <c r="G12">
-        <v>41.58</v>
+        <v>48.32</v>
       </c>
       <c r="H12">
-        <v>24.18</v>
+        <v>24.29</v>
       </c>
       <c r="I12">
-        <v>5.21</v>
+        <v>5.79</v>
       </c>
       <c r="J12">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="K12">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="L12" t="s">
         <v>123</v>
@@ -1369,31 +1381,31 @@
         <v>23</v>
       </c>
       <c r="C13">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E13">
         <v>100</v>
       </c>
       <c r="F13">
-        <v>81</v>
+        <v>81.69</v>
       </c>
       <c r="G13">
-        <v>48.78</v>
+        <v>41.52</v>
       </c>
       <c r="H13">
-        <v>26.32</v>
+        <v>24.12</v>
       </c>
       <c r="I13">
-        <v>13.2</v>
+        <v>5.8</v>
       </c>
       <c r="J13">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="K13">
-        <v>0.62</v>
+        <v>0.77</v>
       </c>
       <c r="L13" t="s">
         <v>124</v>
@@ -1413,22 +1425,22 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>79.01000000000001</v>
+        <v>79.03</v>
       </c>
       <c r="G14">
-        <v>45.07</v>
+        <v>45.13</v>
       </c>
       <c r="H14">
-        <v>24.87</v>
+        <v>24.92</v>
       </c>
       <c r="I14">
-        <v>12.48</v>
+        <v>12.5</v>
       </c>
       <c r="J14">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="K14">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="L14" t="s">
         <v>125</v>
@@ -1448,22 +1460,22 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>78.42</v>
+        <v>78.47</v>
       </c>
       <c r="G15">
         <v>42.93</v>
       </c>
       <c r="H15">
-        <v>23.19</v>
+        <v>23.17</v>
       </c>
       <c r="I15">
-        <v>11.32</v>
+        <v>11.29</v>
       </c>
       <c r="J15">
-        <v>2.46</v>
+        <v>2.71</v>
       </c>
       <c r="K15">
-        <v>0.51</v>
+        <v>0.62</v>
       </c>
       <c r="L15" t="s">
         <v>126</v>
@@ -1483,22 +1495,22 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>74.48</v>
+        <v>74.47</v>
       </c>
       <c r="G16">
-        <v>55.22</v>
+        <v>55.29</v>
       </c>
       <c r="H16">
-        <v>28.9</v>
+        <v>28.89</v>
       </c>
       <c r="I16">
-        <v>4.95</v>
+        <v>5.69</v>
       </c>
       <c r="J16">
-        <v>2.06</v>
+        <v>2.39</v>
       </c>
       <c r="K16">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="L16" t="s">
         <v>127</v>
@@ -1518,22 +1530,22 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>79.09</v>
+        <v>79.11</v>
       </c>
       <c r="G17">
         <v>52.06</v>
       </c>
       <c r="H17">
-        <v>7.39</v>
+        <v>8.42</v>
       </c>
       <c r="I17">
-        <v>3.83</v>
+        <v>4.35</v>
       </c>
       <c r="J17">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="K17">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="L17" t="s">
         <v>128</v>
@@ -1553,22 +1565,22 @@
         <v>100</v>
       </c>
       <c r="F18">
-        <v>73.77</v>
+        <v>73.8</v>
       </c>
       <c r="G18">
-        <v>38.18</v>
+        <v>38.26</v>
       </c>
       <c r="H18">
-        <v>19</v>
+        <v>19.08</v>
       </c>
       <c r="I18">
-        <v>8.81</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J18">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="K18">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="L18" t="s">
         <v>129</v>
@@ -1588,22 +1600,22 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>70.97</v>
+        <v>70.98</v>
       </c>
       <c r="G19">
-        <v>42.12</v>
+        <v>42.1</v>
       </c>
       <c r="H19">
-        <v>6.88</v>
+        <v>7.69</v>
       </c>
       <c r="I19">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="J19">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="K19">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="L19" t="s">
         <v>130</v>
@@ -1623,10 +1635,10 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>68.20999999999999</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="G20">
-        <v>40.45</v>
+        <v>40.5</v>
       </c>
       <c r="H20">
         <v>17.1</v>
@@ -1635,10 +1647,10 @@
         <v>8.09</v>
       </c>
       <c r="J20">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="K20">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="L20" t="s">
         <v>131</v>
@@ -1655,25 +1667,25 @@
         <v>109</v>
       </c>
       <c r="E21">
-        <v>77.3</v>
+        <v>77.23</v>
       </c>
       <c r="F21">
-        <v>34.27</v>
+        <v>34.13</v>
       </c>
       <c r="G21">
-        <v>23.51</v>
+        <v>23.48</v>
       </c>
       <c r="H21">
-        <v>14.39</v>
+        <v>14.36</v>
       </c>
       <c r="I21">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="J21">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="K21">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="L21" t="s">
         <v>132</v>
@@ -1693,22 +1705,22 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>70.86</v>
+        <v>70.81</v>
       </c>
       <c r="G22">
-        <v>28.53</v>
+        <v>28.54</v>
       </c>
       <c r="H22">
-        <v>12.34</v>
+        <v>12.32</v>
       </c>
       <c r="I22">
-        <v>5.19</v>
+        <v>5.21</v>
       </c>
       <c r="J22">
-        <v>0.92</v>
+        <v>1.03</v>
       </c>
       <c r="K22">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L22" t="s">
         <v>133</v>
@@ -1719,31 +1731,31 @@
         <v>33</v>
       </c>
       <c r="C23">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E23">
         <v>100</v>
       </c>
       <c r="F23">
-        <v>61.61</v>
+        <v>62.74</v>
       </c>
       <c r="G23">
-        <v>28.25</v>
+        <v>31.43</v>
       </c>
       <c r="H23">
-        <v>11.31</v>
+        <v>11.74</v>
       </c>
       <c r="I23">
-        <v>1.88</v>
+        <v>4.92</v>
       </c>
       <c r="J23">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="K23">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="L23" t="s">
         <v>134</v>
@@ -1754,31 +1766,31 @@
         <v>34</v>
       </c>
       <c r="C24">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E24">
         <v>100</v>
       </c>
       <c r="F24">
-        <v>62.76</v>
+        <v>61.69</v>
       </c>
       <c r="G24">
-        <v>31.38</v>
+        <v>28.2</v>
       </c>
       <c r="H24">
-        <v>11.72</v>
+        <v>11.29</v>
       </c>
       <c r="I24">
-        <v>4.9</v>
+        <v>2.04</v>
       </c>
       <c r="J24">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="K24">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="L24" t="s">
         <v>135</v>
@@ -1798,22 +1810,22 @@
         <v>100</v>
       </c>
       <c r="F25">
-        <v>70.38</v>
+        <v>70.42</v>
       </c>
       <c r="G25">
-        <v>22.65</v>
+        <v>22.6</v>
       </c>
       <c r="H25">
-        <v>11.3</v>
+        <v>11.27</v>
       </c>
       <c r="I25">
-        <v>4.67</v>
+        <v>4.64</v>
       </c>
       <c r="J25">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="K25">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="L25" t="s">
         <v>136</v>
@@ -1833,22 +1845,22 @@
         <v>100</v>
       </c>
       <c r="F26">
-        <v>64.53</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="G26">
-        <v>23.65</v>
+        <v>23.67</v>
       </c>
       <c r="H26">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="I26">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="J26">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="K26">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="L26" t="s">
         <v>137</v>
@@ -1868,22 +1880,22 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>52.53</v>
+        <v>52.49</v>
       </c>
       <c r="G27">
-        <v>25.17</v>
+        <v>25.15</v>
       </c>
       <c r="H27">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="I27">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="J27">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="K27">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="L27" t="s">
         <v>138</v>
@@ -1903,22 +1915,22 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>69</v>
+        <v>68.95</v>
       </c>
       <c r="G28">
-        <v>23.7</v>
+        <v>23.64</v>
       </c>
       <c r="H28">
-        <v>11.4</v>
+        <v>11.34</v>
       </c>
       <c r="I28">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="J28">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="K28">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="L28" t="s">
         <v>139</v>
@@ -1938,22 +1950,22 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>63.24</v>
+        <v>63.21</v>
       </c>
       <c r="G29">
-        <v>28.29</v>
+        <v>28.26</v>
       </c>
       <c r="H29">
-        <v>2.93</v>
+        <v>3.35</v>
       </c>
       <c r="I29">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="J29">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="K29">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L29" t="s">
         <v>140</v>
@@ -1970,25 +1982,25 @@
         <v>110</v>
       </c>
       <c r="E30">
-        <v>59.81</v>
+        <v>59.83</v>
       </c>
       <c r="F30">
-        <v>30.8</v>
+        <v>30.77</v>
       </c>
       <c r="G30">
-        <v>15.14</v>
+        <v>15.19</v>
       </c>
       <c r="H30">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="I30">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="J30">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="K30">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L30" t="s">
         <v>141</v>
@@ -1999,31 +2011,31 @@
         <v>41</v>
       </c>
       <c r="C31">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s">
         <v>111</v>
       </c>
       <c r="E31">
-        <v>71.91</v>
+        <v>100</v>
       </c>
       <c r="F31">
-        <v>42.53</v>
+        <v>65.31</v>
       </c>
       <c r="G31">
-        <v>12.97</v>
+        <v>24.35</v>
       </c>
       <c r="H31">
-        <v>5.8</v>
+        <v>7.85</v>
       </c>
       <c r="I31">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="J31">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="K31">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L31" t="s">
         <v>142</v>
@@ -2034,31 +2046,31 @@
         <v>42</v>
       </c>
       <c r="C32">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s">
         <v>111</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="F32">
-        <v>65.28</v>
+        <v>42.54</v>
       </c>
       <c r="G32">
-        <v>24.34</v>
+        <v>12.96</v>
       </c>
       <c r="H32">
-        <v>7.81</v>
+        <v>5.79</v>
       </c>
       <c r="I32">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="J32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="K32">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L32" t="s">
         <v>143</v>
@@ -2075,10 +2087,10 @@
         <v>112</v>
       </c>
       <c r="E33">
-        <v>66.39</v>
+        <v>66.42</v>
       </c>
       <c r="F33">
-        <v>16.15</v>
+        <v>16.11</v>
       </c>
       <c r="G33">
         <v>8.640000000000001</v>
@@ -2090,7 +2102,7 @@
         <v>1.61</v>
       </c>
       <c r="J33">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="K33">
         <v>0.04</v>
@@ -2113,22 +2125,22 @@
         <v>100</v>
       </c>
       <c r="F34">
-        <v>60.34</v>
+        <v>60.35</v>
       </c>
       <c r="G34">
-        <v>4.51</v>
+        <v>5.22</v>
       </c>
       <c r="H34">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="I34">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="J34">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="K34">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="L34" t="s">
         <v>145</v>
@@ -2145,25 +2157,25 @@
         <v>110</v>
       </c>
       <c r="E35">
-        <v>51.38</v>
+        <v>51.46</v>
       </c>
       <c r="F35">
-        <v>29.29</v>
+        <v>29.36</v>
       </c>
       <c r="G35">
-        <v>2.76</v>
+        <v>3.14</v>
       </c>
       <c r="H35">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="I35">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="J35">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="K35">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="L35" t="s">
         <v>146</v>
@@ -2183,19 +2195,19 @@
         <v>75.70999999999999</v>
       </c>
       <c r="F36">
-        <v>32.52</v>
+        <v>32.53</v>
       </c>
       <c r="G36">
-        <v>14.09</v>
+        <v>14.07</v>
       </c>
       <c r="H36">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="I36">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="J36">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="K36">
         <v>0.03</v>
@@ -2209,31 +2221,31 @@
         <v>47</v>
       </c>
       <c r="C37">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E37">
-        <v>100</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="F37">
-        <v>62.55</v>
+        <v>31.74</v>
       </c>
       <c r="G37">
-        <v>22.34</v>
+        <v>9.34</v>
       </c>
       <c r="H37">
-        <v>7.22</v>
+        <v>3.01</v>
       </c>
       <c r="I37">
-        <v>0.6899999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="J37">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="K37">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L37" t="s">
         <v>148</v>
@@ -2244,31 +2256,31 @@
         <v>48</v>
       </c>
       <c r="C38">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E38">
-        <v>67.7</v>
+        <v>100</v>
       </c>
       <c r="F38">
-        <v>20.19</v>
+        <v>62.56</v>
       </c>
       <c r="G38">
-        <v>10.88</v>
+        <v>22.34</v>
       </c>
       <c r="H38">
-        <v>3.38</v>
+        <v>7.21</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J38">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="K38">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L38" t="s">
         <v>149</v>
@@ -2279,25 +2291,25 @@
         <v>49</v>
       </c>
       <c r="C39">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E39">
-        <v>48.62</v>
+        <v>67.7</v>
       </c>
       <c r="F39">
-        <v>27.03</v>
+        <v>20.17</v>
       </c>
       <c r="G39">
-        <v>2.46</v>
+        <v>10.84</v>
       </c>
       <c r="H39">
-        <v>1.1</v>
+        <v>3.39</v>
       </c>
       <c r="I39">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="J39">
         <v>0.14</v>
@@ -2306,7 +2318,7 @@
         <v>0.02</v>
       </c>
       <c r="L39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2314,34 +2326,34 @@
         <v>50</v>
       </c>
       <c r="C40">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="D40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E40">
-        <v>77.81</v>
+        <v>48.54</v>
       </c>
       <c r="F40">
-        <v>31.78</v>
+        <v>26.97</v>
       </c>
       <c r="G40">
-        <v>9.300000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="H40">
-        <v>2.98</v>
+        <v>1.21</v>
       </c>
       <c r="I40">
-        <v>0.93</v>
+        <v>0.43</v>
       </c>
       <c r="J40">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="K40">
         <v>0.02</v>
       </c>
       <c r="L40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2349,34 +2361,34 @@
         <v>51</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E41">
-        <v>62.51</v>
+        <v>100</v>
       </c>
       <c r="F41">
-        <v>3.43</v>
+        <v>47.32</v>
       </c>
       <c r="G41">
-        <v>1.88</v>
+        <v>11.26</v>
       </c>
       <c r="H41">
-        <v>0.84</v>
+        <v>4.13</v>
       </c>
       <c r="I41">
-        <v>0.33</v>
+        <v>1.08</v>
       </c>
       <c r="J41">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="K41">
         <v>0.02</v>
       </c>
       <c r="L41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2384,34 +2396,34 @@
         <v>52</v>
       </c>
       <c r="C42">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="D42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E42">
         <v>100</v>
       </c>
       <c r="F42">
-        <v>47.31</v>
+        <v>43.68</v>
       </c>
       <c r="G42">
-        <v>11.27</v>
+        <v>3.73</v>
       </c>
       <c r="H42">
-        <v>4.1</v>
+        <v>1.44</v>
       </c>
       <c r="I42">
-        <v>1.06</v>
+        <v>0.44</v>
       </c>
       <c r="J42">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="K42">
         <v>0.02</v>
       </c>
       <c r="L42" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2419,34 +2431,34 @@
         <v>53</v>
       </c>
       <c r="C43">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E43">
-        <v>100</v>
+        <v>62.55</v>
       </c>
       <c r="F43">
-        <v>43.68</v>
+        <v>3.99</v>
       </c>
       <c r="G43">
-        <v>3.35</v>
+        <v>2.19</v>
       </c>
       <c r="H43">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="I43">
         <v>0.39</v>
       </c>
       <c r="J43">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="K43">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2460,28 +2472,28 @@
         <v>110</v>
       </c>
       <c r="E44">
-        <v>54.19</v>
+        <v>54.35</v>
       </c>
       <c r="F44">
-        <v>21.83</v>
+        <v>21.84</v>
       </c>
       <c r="G44">
-        <v>8.02</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H44">
         <v>2.51</v>
       </c>
       <c r="I44">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="J44">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="K44">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2495,28 +2507,28 @@
         <v>110</v>
       </c>
       <c r="E45">
-        <v>68.37</v>
+        <v>68.3</v>
       </c>
       <c r="F45">
-        <v>19.95</v>
+        <v>19.98</v>
       </c>
       <c r="G45">
-        <v>8.6</v>
+        <v>8.65</v>
       </c>
       <c r="H45">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="I45">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="J45">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="K45">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2530,28 +2542,28 @@
         <v>112</v>
       </c>
       <c r="E46">
-        <v>58.45</v>
+        <v>58.51</v>
       </c>
       <c r="F46">
-        <v>20.36</v>
+        <v>20.33</v>
       </c>
       <c r="G46">
-        <v>8.99</v>
+        <v>8.94</v>
       </c>
       <c r="H46">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="I46">
         <v>0.85</v>
       </c>
       <c r="J46">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="K46">
         <v>0.01</v>
       </c>
       <c r="L46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2559,25 +2571,25 @@
         <v>57</v>
       </c>
       <c r="C47">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D47" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E47">
-        <v>64.53</v>
+        <v>53.5</v>
       </c>
       <c r="F47">
-        <v>26.78</v>
+        <v>12.12</v>
       </c>
       <c r="G47">
-        <v>9.949999999999999</v>
+        <v>5.18</v>
       </c>
       <c r="H47">
-        <v>0.82</v>
+        <v>1.64</v>
       </c>
       <c r="I47">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="J47">
         <v>0.07000000000000001</v>
@@ -2586,7 +2598,7 @@
         <v>0.01</v>
       </c>
       <c r="L47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2600,28 +2612,28 @@
         <v>110</v>
       </c>
       <c r="E48">
-        <v>40.19</v>
+        <v>40.17</v>
       </c>
       <c r="F48">
-        <v>16.67</v>
+        <v>16.74</v>
       </c>
       <c r="G48">
-        <v>6.64</v>
+        <v>6.66</v>
       </c>
       <c r="H48">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="I48">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="J48">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="K48">
         <v>0.01</v>
       </c>
       <c r="L48" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2629,34 +2641,34 @@
         <v>59</v>
       </c>
       <c r="C49">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E49">
-        <v>53.54</v>
+        <v>64.5</v>
       </c>
       <c r="F49">
-        <v>12.2</v>
+        <v>26.84</v>
       </c>
       <c r="G49">
-        <v>5.23</v>
+        <v>9.99</v>
       </c>
       <c r="H49">
-        <v>1.64</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I49">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="J49">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K49">
         <v>0.01</v>
       </c>
       <c r="L49" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2670,19 +2682,19 @@
         <v>109</v>
       </c>
       <c r="E50">
-        <v>67.06</v>
+        <v>67.03</v>
       </c>
       <c r="F50">
-        <v>30.21</v>
+        <v>30.25</v>
       </c>
       <c r="G50">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="H50">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="I50">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="J50">
         <v>0.07000000000000001</v>
@@ -2691,7 +2703,7 @@
         <v>0.01</v>
       </c>
       <c r="L50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2705,28 +2717,28 @@
         <v>111</v>
       </c>
       <c r="E51">
-        <v>66.47</v>
+        <v>66.45</v>
       </c>
       <c r="F51">
-        <v>22.3</v>
+        <v>22.35</v>
       </c>
       <c r="G51">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="H51">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="I51">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="J51">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K51">
         <v>0.01</v>
       </c>
       <c r="L51" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2740,19 +2752,19 @@
         <v>109</v>
       </c>
       <c r="E52">
-        <v>58.45</v>
+        <v>58.49</v>
       </c>
       <c r="F52">
-        <v>16.43</v>
+        <v>16.46</v>
       </c>
       <c r="G52">
-        <v>8.779999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="H52">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="I52">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="J52">
         <v>0.06</v>
@@ -2761,7 +2773,7 @@
         <v>0.01</v>
       </c>
       <c r="L52" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2775,19 +2787,19 @@
         <v>110</v>
       </c>
       <c r="E53">
-        <v>55.67</v>
+        <v>55.64</v>
       </c>
       <c r="F53">
-        <v>17.32</v>
+        <v>17.28</v>
       </c>
       <c r="G53">
-        <v>6.89</v>
+        <v>6.85</v>
       </c>
       <c r="H53">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="I53">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="J53">
         <v>0.06</v>
@@ -2796,7 +2808,7 @@
         <v>0.01</v>
       </c>
       <c r="L53" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2810,28 +2822,28 @@
         <v>110</v>
       </c>
       <c r="E54">
-        <v>45.81</v>
+        <v>45.65</v>
       </c>
       <c r="F54">
-        <v>16.55</v>
+        <v>16.48</v>
       </c>
       <c r="G54">
-        <v>5.51</v>
+        <v>5.45</v>
       </c>
       <c r="H54">
         <v>1.54</v>
       </c>
       <c r="I54">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J54">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K54">
         <v>0.01</v>
       </c>
       <c r="L54" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -2845,13 +2857,13 @@
         <v>111</v>
       </c>
       <c r="E55">
-        <v>46.46</v>
+        <v>46.5</v>
       </c>
       <c r="F55">
-        <v>9.44</v>
+        <v>9.48</v>
       </c>
       <c r="G55">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="H55">
         <v>1.07</v>
@@ -2866,7 +2878,7 @@
         <v>0.01</v>
       </c>
       <c r="L55" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -2874,34 +2886,34 @@
         <v>66</v>
       </c>
       <c r="C56">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="D56" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E56">
-        <v>51.44</v>
+        <v>67.7</v>
       </c>
       <c r="F56">
-        <v>8.56</v>
+        <v>23.14</v>
       </c>
       <c r="G56">
-        <v>3.86</v>
+        <v>4.77</v>
       </c>
       <c r="H56">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="I56">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="J56">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L56" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -2915,28 +2927,28 @@
         <v>112</v>
       </c>
       <c r="E57">
-        <v>57.66</v>
+        <v>57.85</v>
       </c>
       <c r="F57">
-        <v>16.6</v>
+        <v>16.59</v>
       </c>
       <c r="G57">
-        <v>5.24</v>
+        <v>5.27</v>
       </c>
       <c r="H57">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I57">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="J57">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L57" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -2950,16 +2962,16 @@
         <v>110</v>
       </c>
       <c r="E58">
-        <v>50.61</v>
+        <v>50.73</v>
       </c>
       <c r="F58">
-        <v>11.27</v>
+        <v>11.25</v>
       </c>
       <c r="G58">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="H58">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I58">
         <v>0.14</v>
@@ -2968,10 +2980,10 @@
         <v>0.04</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L58" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -2979,34 +2991,34 @@
         <v>69</v>
       </c>
       <c r="C59">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="D59" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E59">
-        <v>49.39</v>
+        <v>51.35</v>
       </c>
       <c r="F59">
-        <v>10.75</v>
+        <v>8.5</v>
       </c>
       <c r="G59">
-        <v>3.46</v>
+        <v>3.82</v>
       </c>
       <c r="H59">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="I59">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="J59">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L59" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3014,34 +3026,34 @@
         <v>70</v>
       </c>
       <c r="C60">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D60" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E60">
-        <v>72.41</v>
+        <v>49.27</v>
       </c>
       <c r="F60">
-        <v>18.35</v>
+        <v>10.7</v>
       </c>
       <c r="G60">
-        <v>5.66</v>
+        <v>3.45</v>
       </c>
       <c r="H60">
-        <v>1.68</v>
+        <v>1.12</v>
       </c>
       <c r="I60">
-        <v>0.42</v>
+        <v>0.13</v>
       </c>
       <c r="J60">
         <v>0.04</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L60" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3049,34 +3061,34 @@
         <v>71</v>
       </c>
       <c r="C61">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="D61" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E61">
-        <v>67.7</v>
+        <v>48.65</v>
       </c>
       <c r="F61">
-        <v>23.19</v>
+        <v>7.68</v>
       </c>
       <c r="G61">
-        <v>4.78</v>
+        <v>3.33</v>
       </c>
       <c r="H61">
-        <v>1.65</v>
+        <v>1.1</v>
       </c>
       <c r="I61">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
       <c r="J61">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K61">
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3084,34 +3096,34 @@
         <v>72</v>
       </c>
       <c r="C62">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D62" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E62">
-        <v>57.12</v>
+        <v>72.56</v>
       </c>
       <c r="F62">
-        <v>21.42</v>
+        <v>18.37</v>
       </c>
       <c r="G62">
-        <v>5.72</v>
+        <v>5.62</v>
       </c>
       <c r="H62">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="I62">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="J62">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3119,34 +3131,34 @@
         <v>73</v>
       </c>
       <c r="C63">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E63">
-        <v>44.33</v>
+        <v>57.06</v>
       </c>
       <c r="F63">
-        <v>11.7</v>
+        <v>21.32</v>
       </c>
       <c r="G63">
-        <v>4.04</v>
+        <v>5.75</v>
       </c>
       <c r="H63">
-        <v>0.32</v>
+        <v>1.34</v>
       </c>
       <c r="I63">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="J63">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3154,34 +3166,34 @@
         <v>74</v>
       </c>
       <c r="C64">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="D64" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E64">
-        <v>48.56</v>
+        <v>54.27</v>
       </c>
       <c r="F64">
-        <v>7.66</v>
+        <v>12.12</v>
       </c>
       <c r="G64">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="H64">
-        <v>1.1</v>
+        <v>0.96</v>
       </c>
       <c r="I64">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J64">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3195,28 +3207,28 @@
         <v>112</v>
       </c>
       <c r="E65">
-        <v>41.55</v>
+        <v>41.49</v>
       </c>
       <c r="F65">
-        <v>11.43</v>
+        <v>11.37</v>
       </c>
       <c r="G65">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="H65">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I65">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="J65">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3224,25 +3236,25 @@
         <v>76</v>
       </c>
       <c r="C66">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D66" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E66">
-        <v>54.3</v>
+        <v>57.07</v>
       </c>
       <c r="F66">
-        <v>12.11</v>
+        <v>19.18</v>
       </c>
       <c r="G66">
-        <v>3.52</v>
+        <v>4.05</v>
       </c>
       <c r="H66">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
       <c r="I66">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="J66">
         <v>0.02</v>
@@ -3251,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3259,25 +3271,25 @@
         <v>77</v>
       </c>
       <c r="C67">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="D67" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E67">
-        <v>62</v>
+        <v>50.03</v>
       </c>
       <c r="F67">
-        <v>12.96</v>
+        <v>18.73</v>
       </c>
       <c r="G67">
-        <v>2.96</v>
+        <v>4.78</v>
       </c>
       <c r="H67">
-        <v>0.8100000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="I67">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J67">
         <v>0.02</v>
@@ -3286,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="L67" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3294,34 +3306,34 @@
         <v>78</v>
       </c>
       <c r="C68">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="D68" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E68">
-        <v>41.55</v>
+        <v>44.36</v>
       </c>
       <c r="F68">
-        <v>9.09</v>
+        <v>11.74</v>
       </c>
       <c r="G68">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="H68">
-        <v>1.02</v>
+        <v>0.35</v>
       </c>
       <c r="I68">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J68">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3329,25 +3341,25 @@
         <v>79</v>
       </c>
       <c r="C69">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E69">
-        <v>57.1</v>
+        <v>62.08</v>
       </c>
       <c r="F69">
-        <v>19.14</v>
+        <v>12.98</v>
       </c>
       <c r="G69">
-        <v>4.06</v>
+        <v>2.99</v>
       </c>
       <c r="H69">
-        <v>1.34</v>
+        <v>0.83</v>
       </c>
       <c r="I69">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="J69">
         <v>0.02</v>
@@ -3356,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="L69" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3364,34 +3376,34 @@
         <v>80</v>
       </c>
       <c r="C70">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E70">
-        <v>33.61</v>
+        <v>41.51</v>
       </c>
       <c r="F70">
-        <v>4.72</v>
+        <v>9.07</v>
       </c>
       <c r="G70">
-        <v>1.75</v>
+        <v>4.07</v>
       </c>
       <c r="H70">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="I70">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="J70">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3405,16 +3417,16 @@
         <v>112</v>
       </c>
       <c r="E71">
-        <v>59.89</v>
+        <v>59.74</v>
       </c>
       <c r="F71">
-        <v>12.78</v>
+        <v>12.76</v>
       </c>
       <c r="G71">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="H71">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I71">
         <v>0.22</v>
@@ -3426,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="L71" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3434,25 +3446,25 @@
         <v>82</v>
       </c>
       <c r="C72">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="D72" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E72">
-        <v>50</v>
+        <v>33.58</v>
       </c>
       <c r="F72">
-        <v>18.74</v>
+        <v>4.71</v>
       </c>
       <c r="G72">
-        <v>4.79</v>
+        <v>1.75</v>
       </c>
       <c r="H72">
-        <v>1.09</v>
+        <v>0.58</v>
       </c>
       <c r="I72">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="J72">
         <v>0.01</v>
@@ -3461,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="L72" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3469,25 +3481,25 @@
         <v>83</v>
       </c>
       <c r="C73">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E73">
-        <v>42.34</v>
+        <v>37.45</v>
       </c>
       <c r="F73">
-        <v>9.640000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="G73">
-        <v>2.49</v>
+        <v>0.65</v>
       </c>
       <c r="H73">
-        <v>0.58</v>
+        <v>0.22</v>
       </c>
       <c r="I73">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="J73">
         <v>0.01</v>
@@ -3496,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="L73" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3504,25 +3516,25 @@
         <v>84</v>
       </c>
       <c r="C74">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D74" t="s">
         <v>109</v>
       </c>
       <c r="E74">
-        <v>52.89</v>
+        <v>49.97</v>
       </c>
       <c r="F74">
-        <v>11.53</v>
+        <v>18.7</v>
       </c>
       <c r="G74">
-        <v>4.09</v>
+        <v>4.75</v>
       </c>
       <c r="H74">
-        <v>0.25</v>
+        <v>1.09</v>
       </c>
       <c r="I74">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="J74">
         <v>0.01</v>
@@ -3531,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3539,25 +3551,25 @@
         <v>85</v>
       </c>
       <c r="C75">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="D75" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E75">
-        <v>54.89</v>
+        <v>22.77</v>
       </c>
       <c r="F75">
-        <v>7.39</v>
+        <v>4.34</v>
       </c>
       <c r="G75">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="H75">
-        <v>0.41</v>
+        <v>0.59</v>
       </c>
       <c r="I75">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="J75">
         <v>0.01</v>
@@ -3566,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="L75" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3574,22 +3586,22 @@
         <v>86</v>
       </c>
       <c r="C76">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D76" t="s">
         <v>112</v>
       </c>
       <c r="E76">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="F76">
-        <v>8.880000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G76">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="H76">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="I76">
         <v>0.12</v>
@@ -3601,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3609,25 +3621,25 @@
         <v>87</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s">
         <v>109</v>
       </c>
       <c r="E77">
-        <v>37.49</v>
+        <v>52.86</v>
       </c>
       <c r="F77">
-        <v>1.32</v>
+        <v>11.51</v>
       </c>
       <c r="G77">
-        <v>0.57</v>
+        <v>4.06</v>
       </c>
       <c r="H77">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="I77">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J77">
         <v>0.01</v>
@@ -3636,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="L77" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3644,34 +3656,34 @@
         <v>88</v>
       </c>
       <c r="C78">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D78" t="s">
         <v>109</v>
       </c>
       <c r="E78">
-        <v>47.11</v>
+        <v>35.5</v>
       </c>
       <c r="F78">
-        <v>9.390000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G78">
-        <v>3.09</v>
+        <v>2.54</v>
       </c>
       <c r="H78">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="I78">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="J78">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K78">
         <v>0</v>
       </c>
       <c r="L78" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3679,25 +3691,25 @@
         <v>89</v>
       </c>
       <c r="C79">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D79" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E79">
-        <v>50</v>
+        <v>42.94</v>
       </c>
       <c r="F79">
-        <v>18.71</v>
+        <v>13.37</v>
       </c>
       <c r="G79">
-        <v>4.78</v>
+        <v>2.94</v>
       </c>
       <c r="H79">
-        <v>1.07</v>
+        <v>0.54</v>
       </c>
       <c r="I79">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J79">
         <v>0.01</v>
@@ -3706,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="L79" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3714,25 +3726,25 @@
         <v>90</v>
       </c>
       <c r="C80">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="D80" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E80">
-        <v>22.7</v>
+        <v>45.73</v>
       </c>
       <c r="F80">
-        <v>4.34</v>
+        <v>8.85</v>
       </c>
       <c r="G80">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="H80">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="I80">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="J80">
         <v>0.01</v>
@@ -3741,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3749,25 +3761,25 @@
         <v>91</v>
       </c>
       <c r="C81">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D81" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E81">
-        <v>42.88</v>
+        <v>42.93</v>
       </c>
       <c r="F81">
-        <v>13.3</v>
+        <v>11.87</v>
       </c>
       <c r="G81">
-        <v>2.92</v>
+        <v>2.01</v>
       </c>
       <c r="H81">
         <v>0.5600000000000001</v>
       </c>
       <c r="I81">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="J81">
         <v>0.01</v>
@@ -3776,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3784,34 +3796,34 @@
         <v>92</v>
       </c>
       <c r="C82">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D82" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E82">
-        <v>42.9</v>
+        <v>28.15</v>
       </c>
       <c r="F82">
-        <v>11.86</v>
+        <v>10.13</v>
       </c>
       <c r="G82">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="H82">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="I82">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K82">
         <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3819,34 +3831,34 @@
         <v>93</v>
       </c>
       <c r="C83">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D83" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E83">
-        <v>35.47</v>
+        <v>32.3</v>
       </c>
       <c r="F83">
-        <v>9.98</v>
+        <v>5.51</v>
       </c>
       <c r="G83">
-        <v>2.53</v>
+        <v>1.98</v>
       </c>
       <c r="H83">
-        <v>0.13</v>
+        <v>0.37</v>
       </c>
       <c r="I83">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K83">
         <v>0</v>
       </c>
       <c r="L83" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3854,25 +3866,25 @@
         <v>94</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D84" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E84">
-        <v>32.94</v>
+        <v>33.55</v>
       </c>
       <c r="F84">
-        <v>9.449999999999999</v>
+        <v>6.83</v>
       </c>
       <c r="G84">
-        <v>0.35</v>
+        <v>1.1</v>
       </c>
       <c r="H84">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="I84">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -3881,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="L84" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -3889,25 +3901,25 @@
         <v>95</v>
       </c>
       <c r="C85">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D85" t="s">
         <v>111</v>
       </c>
       <c r="E85">
-        <v>28.09</v>
+        <v>54.99</v>
       </c>
       <c r="F85">
-        <v>10.16</v>
+        <v>7.35</v>
       </c>
       <c r="G85">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="H85">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="I85">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J85">
         <v>0.01</v>
@@ -3916,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -3924,25 +3936,25 @@
         <v>96</v>
       </c>
       <c r="C86">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E86">
-        <v>31.63</v>
+        <v>40.26</v>
       </c>
       <c r="F86">
-        <v>5.13</v>
+        <v>6.25</v>
       </c>
       <c r="G86">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="H86">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="I86">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -3951,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="L86" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -3959,25 +3971,25 @@
         <v>97</v>
       </c>
       <c r="C87">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E87">
-        <v>66.52</v>
+        <v>47.14</v>
       </c>
       <c r="F87">
-        <v>2.1</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G87">
-        <v>0.61</v>
+        <v>3.08</v>
       </c>
       <c r="H87">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="I87">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="J87">
         <v>0.01</v>
@@ -3986,7 +3998,7 @@
         <v>0</v>
       </c>
       <c r="L87" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -3994,25 +4006,25 @@
         <v>98</v>
       </c>
       <c r="C88">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D88" t="s">
         <v>111</v>
       </c>
       <c r="E88">
-        <v>32.3</v>
+        <v>45.01</v>
       </c>
       <c r="F88">
-        <v>5.48</v>
+        <v>5.08</v>
       </c>
       <c r="G88">
-        <v>1.96</v>
+        <v>1.29</v>
       </c>
       <c r="H88">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="I88">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -4021,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4029,25 +4041,25 @@
         <v>99</v>
       </c>
       <c r="C89">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="D89" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E89">
-        <v>33.53</v>
+        <v>24.29</v>
       </c>
       <c r="F89">
-        <v>6.83</v>
+        <v>4.72</v>
       </c>
       <c r="G89">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="H89">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="I89">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -4056,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="L89" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4064,25 +4076,25 @@
         <v>100</v>
       </c>
       <c r="C90">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="D90" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E90">
-        <v>45.11</v>
+        <v>31.7</v>
       </c>
       <c r="F90">
-        <v>5.12</v>
+        <v>5.14</v>
       </c>
       <c r="G90">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="H90">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I90">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -4091,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4099,25 +4111,25 @@
         <v>101</v>
       </c>
       <c r="C91">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="D91" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E91">
-        <v>32.3</v>
+        <v>66.5</v>
       </c>
       <c r="F91">
-        <v>6.44</v>
+        <v>2.37</v>
       </c>
       <c r="G91">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H91">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I91">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -4126,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4134,26 +4146,26 @@
         <v>102</v>
       </c>
       <c r="C92">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="D92" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E92">
-        <v>33.48</v>
+        <v>27.44</v>
       </c>
       <c r="F92">
-        <v>0.61</v>
+        <v>3.16</v>
       </c>
       <c r="G92">
-        <v>0.11</v>
+        <v>0.5</v>
       </c>
       <c r="H92">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I92">
         <v>0.01</v>
       </c>
-      <c r="I92">
-        <v>0</v>
-      </c>
       <c r="J92">
         <v>0</v>
       </c>
@@ -4161,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4196,33 +4208,33 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D94" t="s">
         <v>109</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>32.97</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -4231,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4239,7 +4251,7 @@
         <v>103</v>
       </c>
       <c r="C95">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D95" t="s">
         <v>109</v>
@@ -4266,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4274,7 +4286,7 @@
         <v>103</v>
       </c>
       <c r="C96">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D96" t="s">
         <v>109</v>
@@ -4301,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4309,7 +4321,7 @@
         <v>103</v>
       </c>
       <c r="C97">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D97" t="s">
         <v>109</v>
@@ -4336,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4344,7 +4356,7 @@
         <v>103</v>
       </c>
       <c r="C98">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D98" t="s">
         <v>109</v>
@@ -4371,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4379,7 +4391,7 @@
         <v>103</v>
       </c>
       <c r="C99">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D99" t="s">
         <v>109</v>
@@ -4406,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4414,7 +4426,7 @@
         <v>103</v>
       </c>
       <c r="C100">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D100" t="s">
         <v>109</v>
@@ -4441,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4449,10 +4461,10 @@
         <v>103</v>
       </c>
       <c r="C101">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D101" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -4476,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="L101" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4484,7 +4496,7 @@
         <v>103</v>
       </c>
       <c r="C102">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D102" t="s">
         <v>111</v>
@@ -4511,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="L102" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4519,7 +4531,7 @@
         <v>103</v>
       </c>
       <c r="C103">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D103" t="s">
         <v>111</v>
@@ -4546,7 +4558,7 @@
         <v>0</v>
       </c>
       <c r="L103" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4554,7 +4566,7 @@
         <v>103</v>
       </c>
       <c r="C104">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D104" t="s">
         <v>111</v>
@@ -4581,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="L104" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4589,7 +4601,7 @@
         <v>103</v>
       </c>
       <c r="C105">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D105" t="s">
         <v>111</v>
@@ -4616,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="L105" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4624,7 +4636,7 @@
         <v>103</v>
       </c>
       <c r="C106">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D106" t="s">
         <v>111</v>
@@ -4651,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="L106" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -4659,7 +4671,7 @@
         <v>103</v>
       </c>
       <c r="C107">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D107" t="s">
         <v>111</v>
@@ -4686,33 +4698,33 @@
         <v>0</v>
       </c>
       <c r="L107" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C108">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D108" t="s">
         <v>111</v>
       </c>
       <c r="E108">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="F108">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="G108">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="H108">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I108">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -4721,33 +4733,33 @@
         <v>0</v>
       </c>
       <c r="L108" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C109">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D109" t="s">
         <v>111</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>22.24</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I109">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -4756,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -4764,10 +4776,10 @@
         <v>103</v>
       </c>
       <c r="C110">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D110" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4791,33 +4803,33 @@
         <v>0</v>
       </c>
       <c r="L110" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C111">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D111" t="s">
         <v>112</v>
       </c>
       <c r="E111">
-        <v>27.59</v>
+        <v>0</v>
       </c>
       <c r="F111">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="G111">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="H111">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I111">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -4826,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="L111" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -4861,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="L112" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -4896,33 +4908,33 @@
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C114">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D114" t="s">
         <v>112</v>
       </c>
       <c r="E114">
-        <v>40.11</v>
+        <v>0</v>
       </c>
       <c r="F114">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="G114">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="H114">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="I114">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -4931,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="L114" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -4939,7 +4951,7 @@
         <v>103</v>
       </c>
       <c r="C115">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D115" t="s">
         <v>112</v>
@@ -4966,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="L115" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -4974,7 +4986,7 @@
         <v>103</v>
       </c>
       <c r="C116">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D116" t="s">
         <v>112</v>
@@ -5001,33 +5013,33 @@
         <v>0</v>
       </c>
       <c r="L116" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C117">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D117" t="s">
         <v>112</v>
       </c>
       <c r="E117">
-        <v>24.29</v>
+        <v>0</v>
       </c>
       <c r="F117">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="I117">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -5036,33 +5048,33 @@
         <v>0</v>
       </c>
       <c r="L117" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C118">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D118" t="s">
         <v>112</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -5071,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="L118" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -5079,7 +5091,7 @@
         <v>103</v>
       </c>
       <c r="C119">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D119" t="s">
         <v>112</v>
@@ -5106,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="L119" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -5114,10 +5126,10 @@
         <v>103</v>
       </c>
       <c r="C120">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D120" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -5141,33 +5153,33 @@
         <v>0</v>
       </c>
       <c r="L120" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C121">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D121" t="s">
         <v>110</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>37.92</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I121">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -5176,33 +5188,33 @@
         <v>0</v>
       </c>
       <c r="L121" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C122">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D122" t="s">
         <v>110</v>
       </c>
       <c r="E122">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F122">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="I122">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -5211,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="L122" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5219,7 +5231,7 @@
         <v>103</v>
       </c>
       <c r="C123">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D123" t="s">
         <v>110</v>
@@ -5246,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="L123" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5254,7 +5266,7 @@
         <v>103</v>
       </c>
       <c r="C124">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D124" t="s">
         <v>110</v>
@@ -5281,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="L124" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5289,7 +5301,7 @@
         <v>103</v>
       </c>
       <c r="C125">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D125" t="s">
         <v>110</v>
@@ -5316,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="L125" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5324,7 +5336,7 @@
         <v>103</v>
       </c>
       <c r="C126">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D126" t="s">
         <v>110</v>
@@ -5351,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="L126" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5359,7 +5371,7 @@
         <v>103</v>
       </c>
       <c r="C127">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D127" t="s">
         <v>110</v>
@@ -5386,30 +5398,30 @@
         <v>0</v>
       </c>
       <c r="L127" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C128">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D128" t="s">
         <v>110</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>33.5</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -5421,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="L128" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -5456,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="L129" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
